--- a/files/九龙-启德-沄璟.xlsx
+++ b/files/九龙-启德-沄璟.xlsx
@@ -4032,27 +4032,23 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>91462500</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>48910</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4082,27 +4078,23 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>97037500</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>50832</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4800,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1870</v>
+        <v>1816</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -4817,14 +4809,14 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
         <v>90860500</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>48589</v>
+        <v>50033</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -29037,7 +29029,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>16 套</t>
+          <t>14 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -29047,7 +29039,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>37 套</t>
+          <t>39 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -29199,7 +29191,30 @@
           <t>30/F</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9,704万
+$50,832/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9,146万
+$48,910/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>29/F</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 招标单位
@@ -29207,7 +29222,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -29216,13 +29231,36 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>28/F</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+暂无价格
+暂无呎价
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+暂无价格
+暂无呎价
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>27/F</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 招标单位
@@ -29230,7 +29268,30 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8,415万
+$45,000/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>26/F</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9,434万
+$49,421/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -29239,67 +29300,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>25/F</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8,415万
-$45,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-$9,434万
-$49,421/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
+$9,490万
+$49,712/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -29308,21 +29323,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>23/F</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
-$9,490万
-$49,712/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
+$8,880万
+$46,517/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -29331,21 +29346,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>22/F</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
-$8,880万
-$46,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+$9,295万
+$48,690/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -29354,29 +29369,6 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-$9,295万
-$48,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="65" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -29393,10 +29385,10 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>B | 1870呎 (4+房)
+          <t>B | 1816呎 (4+房)
 $9,086万
-$48,589/呎
-(26年-06月)</t>
+$50,033/呎
+(已售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-沄璟.xlsx
+++ b/files/九龙-启德-沄璟.xlsx
@@ -8,6 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +49,132 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +185,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +272,81 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +723,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -27745,4 +27994,7104 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>36&amp;37</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3442呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 3138呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12605万
+$60,370/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12522万
+$59,970/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12446万
+$59,609/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$11761万
+$56,327/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9483万
+$50,710/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12055万
+$57,737/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8796万
+$47,036/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$11467万
+$54,916/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9233万
+$49,376/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10557万
+$50,561/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12038万
+$57,653/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9278万
+$49,617/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10255万
+$49,113/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8013万
+$42,850/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10110万
+$48,419/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$9054万
+$49,856/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10252万
+$49,100/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8578万
+$45,870/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10085万
+$48,300/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8929万
+$47,748/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10117万
+$48,453/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8690万
+$46,470/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9855万
+$47,200/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8308万
+$44,429/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9587万
+$45,913/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8207万
+$43,889/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9324万
+$44,653/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8477万
+$45,333/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9542万
+$45,700/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7386万
+$39,500/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9420万
+$45,115/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7939万
+$42,457/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$8403万
+$40,242/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7315万
+$39,120/呎
+(23年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$8456万
+$40,500/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7143万
+$38,200/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9271万
+$44,400/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8182万
+$43,753/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9703万
+$46,472/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7750万
+$41,444/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9127万
+$43,710/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7696万
+$41,157/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$9427万
+$45,150/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7684万
+$41,089/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+$8658万
+$43,617/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 1797呎 (4+房)
+$7178万
+$39,946/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>36&amp;37</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3406呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 3137呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9704万
+$50,832/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9146万
+$48,910/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8415万
+$45,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9434万
+$49,421/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9490万
+$49,712/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8880万
+$46,517/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9295万
+$48,690/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9015万
+$47,221/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$9086万
+$50,033/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9017万
+$47,236/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8552万
+$44,800/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8265万
+$44,200/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8837万
+$46,290/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8302万
+$43,490/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8103万
+$43,329/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7865万
+$41,200/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7667万
+$41,000/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7770万
+$40,700/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7574万
+$40,500/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8062万
+$42,231/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8054万
+$43,070/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8319万
+$43,579/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7630万
+$40,800/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7882万
+$41,290/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7904万
+$42,270/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7470万
+$39,130/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7860万
+$42,029/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8131万
+$42,595/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7800万
+$41,710/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8104万
+$42,453/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8167万
+$43,673/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7708万
+$40,377/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7532万
+$40,276/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7292万
+$38,200/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7704万
+$41,196/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7576万
+$39,687/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7996万
+$42,757/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 1828呎 (4+房)
+$7534万
+$41,213/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 1797呎 (4+房)
+$7380万
+$41,069/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1129呎 (3房)
+$5215万
+$46,195/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1334呎 (3房)
+$3869万
+$29,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="E5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1546万
+$26,800/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1391万
+$25,100/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1512万
+$26,200/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1363万
+$24,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1489万
+$25,810/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1324万
+$23,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1482万
+$25,681/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1319万
+$23,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1474万
+$25,554/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1341万
+$24,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1467万
+$25,426/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1460万
+$25,300/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1319万
+$23,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1469万
+$25,454/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1285万
+$23,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1196万
+$23,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1438万
+$24,925/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1274万
+$23,000/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1191万
+$23,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1431万
+$24,801/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1269万
+$22,900/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1186万
+$23,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1424万
+$24,677/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 553呎 (2房)
+$1302万
+$23,542/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1417万
+$24,555/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1280万
+$23,100/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1410万
+$24,432/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 553呎 (2房)
+$1274万
+$23,042/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1403万
+$24,311/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 553呎 (2房)
+$1285万
+$23,242/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1411万
+$24,459/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1280万
+$23,100/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1389万
+$24,070/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1274万
+$23,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1382万
+$23,950/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 553呎 (2房)
+$1274万
+$23,042/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1368万
+$23,713/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1258万
+$22,700/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1155万
+$22,700/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1361万
+$23,595/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1252万
+$22,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1150万
+$22,600/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1355万
+$23,477/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1295万
+$23,377/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1348万
+$23,361/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1252万
+$22,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1341万
+$23,244/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1335万
+$23,129/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1235万
+$22,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1247万
+$21,606/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1210万
+$20,976/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1198万
+$20,769/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1195万
+$20,706/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1191万
+$20,644/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 539呎 (2房)
+$1197万
+$22,200/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1109呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1799万
+$27,300/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1423万
+$27,200/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1551万
+$27,300/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1766万
+$26,800/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1396万
+$26,700/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1522万
+$26,800/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1746万
+$26,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1381万
+$26,400/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1505万
+$26,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1735万
+$26,323/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1371万
+$26,205/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 1644呎 (2房)
+$1496万
+$9,099/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1726万
+$26,192/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1364万
+$26,075/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1488万
+$26,205/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1717万
+$26,062/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1357万
+$25,945/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1481万
+$26,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1709万
+$25,932/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1350万
+$25,816/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1474万
+$25,945/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1700万
+$25,803/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1343万
+$25,688/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1466万
+$25,816/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1692万
+$25,675/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1337万
+$25,560/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1459万
+$25,688/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1675万
+$25,421/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1324万
+$25,307/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1445万
+$25,433/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1667万
+$25,294/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1317万
+$25,181/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1437万
+$25,307/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1659万
+$25,168/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1310万
+$25,056/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1430万
+$25,181/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1650万
+$25,043/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1304万
+$24,931/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1423万
+$25,056/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1642万
+$24,919/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1297万
+$24,807/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1416万
+$24,931/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 659呎 (2房)
+$1634万
+$24,795/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+$1291万
+$24,684/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1409万
+$24,807/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1618万
+$24,671/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1292万
+$24,561/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1402万
+$24,684/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1610万
+$24,549/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1285万
+$24,439/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1395万
+$24,561/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1602万
+$24,427/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1279万
+$24,317/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1388万
+$24,439/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1587万
+$24,185/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1266万
+$24,076/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1374万
+$24,197/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1579万
+$24,064/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1260万
+$23,956/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1368万
+$24,076/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1571万
+$23,945/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1254万
+$23,837/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1376万
+$24,223/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1563万
+$23,825/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1248万
+$23,719/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1354万
+$23,837/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1555万
+$23,707/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1241万
+$23,601/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1347万
+$23,719/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1547万
+$23,589/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1235万
+$23,483/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1355万
+$23,863/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1429万
+$21,790/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1158万
+$22,014/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1250万
+$22,014/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1361万
+$20,752/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1103万
+$20,966/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1191万
+$20,966/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1335万
+$20,345/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1081万
+$20,555/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1179万
+$20,758/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1331万
+$20,284/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1078万
+$20,493/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1176万
+$20,696/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (2房)
+$1327万
+$20,223/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1075万
+$20,432/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1172万
+$20,634/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 618呎 (2房)
+$1259万
+$20,371/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 488呎 (2房)
+$1014万
+$20,787/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 530呎 (2房)
+$1166万
+$22,000/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1994呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$3070万
+$33,998/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1884万
+$33,400/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1978万
+$31,900/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$3043万
+$33,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1844万
+$32,700/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1941万
+$31,300/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 900呎 (3房)
+$3043万
+$33,812/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1827万
+$32,400/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1916万
+$30,900/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2935万
+$32,500/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1816万
+$32,200/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1904万
+$30,712/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2946万
+$32,623/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1805万
+$32,000/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1914万
+$30,868/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2899万
+$32,100/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1794万
+$31,800/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1902万
+$30,684/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2935万
+$32,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1782万
+$31,600/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1870万
+$30,165/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2862万
+$31,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1771万
+$31,400/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1859万
+$29,985/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2872万
+$31,805/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1760万
+$31,200/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1848万
+$29,807/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2946万
+$32,630/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1779万
+$31,534/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1828万
+$29,482/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$3180万
+$35,217/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1687万
+$29,917/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1781万
+$28,732/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2781万
+$30,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1719万
+$30,482/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1790万
+$28,878/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2798万
+$30,982/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1709万
+$30,300/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1780万
+$28,706/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2745万
+$30,400/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1699万
+$30,119/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1769万
+$28,534/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 903呎 (3房)
+$2764万
+$30,604/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$1689万
+$29,939/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 620呎 (2房)
+$1759万
+$28,364/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2867万
+$31,785/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1725万
+$30,422/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1726万
+$27,885/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2697万
+$29,900/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1677万
+$29,583/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1716万
+$27,719/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2679万
+$29,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1667万
+$29,407/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1725万
+$27,860/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2661万
+$29,500/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1627万
+$28,693/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1706万
+$27,557/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2634万
+$29,200/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1617万
+$28,522/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1677万
+$27,091/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2713万
+$30,082/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1590万
+$28,040/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1700万
+$27,468/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2970万
+$32,924/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1598万
+$28,183/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1657万
+$26,769/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2589万
+$28,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1588万
+$28,014/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1647万
+$26,609/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2571万
+$28,500/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1562万
+$27,541/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1637万
+$26,451/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2526万
+$28,000/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1442万
+$25,438/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1530万
+$24,714/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$2089万
+$23,156/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1299万
+$22,917/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1391万
+$22,468/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$1989万
+$22,053/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1238万
+$21,826/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1337万
+$21,604/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$1983万
+$21,987/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1234万
+$21,760/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1333万
+$21,539/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 902呎 (3房)
+$1977万
+$21,921/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+$1230万
+$21,695/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 619呎 (2房)
+$1329万
+$21,474/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 869呎 (3房)
+$1921万
+$22,106/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+$1165万
+$22,027/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 597呎 (2房)
+$1292万
+$21,644/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 2103呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3515万
+$37,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2761万
+$35,350/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3133万
+$34,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3397万
+$35,754/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2706万
+$34,643/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3101万
+$34,340/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3473万
+$36,554/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2773万
+$35,510/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3043万
+$33,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3914万
+$41,198/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2666万
+$34,138/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3025万
+$33,500/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3539万
+$37,254/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2646万
+$33,880/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3010万
+$33,330/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3711万
+$39,061/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2609万
+$33,400/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2989万
+$33,100/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3671万
+$38,638/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2708万
+$34,674/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3340万
+$36,992/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3223万
+$33,928/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2708万
+$34,677/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2953万
+$32,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3211万
+$33,800/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2562万
+$32,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3046万
+$33,734/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3618万
+$38,084/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2530万
+$32,399/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2888万
+$31,977/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3154万
+$33,200/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2550万
+$32,650/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2938万
+$32,538/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3480万
+$36,628/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2534万
+$32,445/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3217万
+$35,626/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3221万
+$33,902/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2491万
+$31,900/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2936万
+$32,514/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3200万
+$33,687/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2476万
+$31,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2835万
+$31,400/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 950呎 (3房)
+$3564万
+$37,513/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 781呎 (3房)
+$2460万
+$31,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2817万
+$31,200/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$3334万
+$35,165/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2980万
+$38,010/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2742万
+$30,399/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$3268万
+$34,473/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2465万
+$31,444/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$3120万
+$34,591/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$3181万
+$33,555/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2446万
+$31,200/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$3028万
+$33,568/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$3002万
+$31,667/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2447万
+$31,211/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2760万
+$30,599/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2967万
+$31,300/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2564万
+$32,702/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2756万
+$30,550/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2948万
+$31,100/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2376万
+$30,300/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$3070万
+$34,034/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2959万
+$31,209/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2670万
+$34,051/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2733万
+$30,300/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2920万
+$30,800/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2344万
+$29,900/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2670万
+$29,600/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$3151万
+$33,235/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2398万
+$30,590/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2670万
+$29,596/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2702万
+$28,500/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$2242万
+$28,600/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2598万
+$28,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2291万
+$24,163/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$1850万
+$23,596/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2152万
+$23,856/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2141万
+$22,582/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$1745万
+$22,260/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2030万
+$22,506/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2130万
+$22,469/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$1740万
+$22,194/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2024万
+$22,438/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2119万
+$22,357/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+$1735万
+$22,127/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2018万
+$22,371/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$2060万
+$22,518/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 738呎 (3房)
+$1680万
+$22,764/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 869呎 (3房)
+$1960万
+$22,560/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2729呎 (4+房)
+$16224万
+$59,449/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$6543万
+$42,959/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4953万
+$41,725/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5742万
+$37,700/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4522万
+$38,100/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5966万
+$39,174/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$5074万
+$42,743/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5528万
+$36,300/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4439万
+$37,400/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5498万
+$36,100/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4439万
+$37,400/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5969万
+$39,190/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4380万
+$36,900/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5986万
+$39,307/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4356万
+$36,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5840万
+$38,346/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4321万
+$36,400/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5457万
+$35,830/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4285万
+$36,100/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5393万
+$35,410/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4500万
+$37,911/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5313万
+$34,882/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1135呎 (3房)
+$4214万
+$37,126/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5474万
+$35,942/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4851万
+$40,867/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5387万
+$35,369/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4330万
+$36,477/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$4980万
+$32,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$3960万
+$33,361/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5364万
+$35,217/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4095万
+$34,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4926万
+$32,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4206万
+$35,494/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4956万
+$32,498/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4468万
+$37,705/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5002万
+$32,800/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4005万
+$33,800/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5265万
+$34,525/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4092万
+$34,531/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4773万
+$31,300/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3922万
+$33,100/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5261万
+$34,497/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4100万
+$34,599/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5101万
+$33,450/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4337万
+$36,596/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4712万
+$30,900/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4039万
+$34,084/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5119万
+$33,566/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4317万
+$36,433/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4888万
+$32,050/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3389万
+$28,600/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4333万
+$28,410/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3300万
+$27,848/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4049万
+$26,552/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3261万
+$27,522/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4380万
+$28,720/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3072万
+$25,920/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4376万
+$28,692/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$2978万
+$25,131/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 1466呎 (3房)
+$4217万
+$28,768/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 1146呎 (3房)
+$2904万
+$25,336/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>沄璟 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>6 套</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>4 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/屋号</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Harbour Breeze</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Harbour Light</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Harbour Wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mansion A</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Mansion A (Harbour Light)
+4837呎 (4+房)
+(24年-07月)
+$3.80亿
+$78,561/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr"/>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Mansion B</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Mansion B (Harbour Breeze)
+4355呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Mansion C</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr"/>
+      <c r="C8" s="30" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Mansion C (Harbour Wave)
+4378呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-沄璟.xlsx
+++ b/files/九龙-启德-沄璟.xlsx
@@ -723,7 +723,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -35043,10 +35043,10 @@
       <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Mansion A (Harbour Light)
-4837呎 (4+房)
-(24年-07月)
-$3.80亿
-$78,561/呎</t>
+4636呎 (4+房)
+(24年-06月)
+$3.40亿
+$73,339/呎</t>
         </is>
       </c>
       <c r="D6" s="30" t="inlineStr"/>
@@ -35060,7 +35060,7 @@
       <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Mansion B (Harbour Breeze)
-4355呎 (4+房)
+4294呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -35080,7 +35080,7 @@
       <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Mansion C (Harbour Wave)
-4378呎 (4+房)
+4850呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>

--- a/files/九龙-启德-沄璟.xlsx
+++ b/files/九龙-启德-沄璟.xlsx
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>1870</v>
+        <v>1816</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>79955000</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>42757</v>
+        <v>44028</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>79955000</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>42757</v>
+        <v>44028</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>13185200</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>23800</v>
+        <v>23843</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>13185200</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>23800</v>
+        <v>23843</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -10162,14 +10162,14 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
         <v>13406800</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>24200</v>
+        <v>24244</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>13406800</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>24200</v>
+        <v>24244</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -10421,38 +10421,30 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>13351400</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>24100</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K151" s="5" t="n">
+        <v>13351400</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>24100</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10461,7 +10453,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13041,7 +13033,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -13057,7 +13049,7 @@
         <v>12742000</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>23000</v>
+        <v>23042</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -13068,7 +13060,7 @@
         <v>12742000</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>23000</v>
+        <v>23042</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -13508,7 +13500,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13817,7 +13809,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13833,7 +13825,7 @@
         <v>12520400</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>22600</v>
+        <v>22641</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13844,7 +13836,7 @@
         <v>12520400</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>22600</v>
+        <v>22641</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -37957,7 +37949,7 @@
           <t>A | 2088呎 (4+房)
 $12605万
 $60,370/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -37980,7 +37972,7 @@
           <t>A | 2034呎 (4+房)
 $12522万
 $61,562/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -38003,7 +37995,7 @@
           <t>A | 2088呎 (4+房)
 $12446万
 $59,609/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -38049,7 +38041,7 @@
           <t>A | 2088呎 (4+房)
 $11761万
 $56,327/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38057,7 +38049,7 @@
           <t>B | 1870呎 (4+房)
 $9483万
 $50,710/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -38072,7 +38064,7 @@
           <t>A | 2088呎 (4+房)
 $12055万
 $57,737/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38080,7 +38072,7 @@
           <t>B | 1870呎 (4+房)
 $8796万
 $47,036/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -38095,7 +38087,7 @@
           <t>A | 2088呎 (4+房)
 $11467万
 $54,916/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38103,7 +38095,7 @@
           <t>B | 1870呎 (4+房)
 $9233万
 $49,376/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -38118,7 +38110,7 @@
           <t>A | 2088呎 (4+房)
 $10557万
 $50,561/呎
-(23年-02月-07日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -38141,7 +38133,7 @@
           <t>A | 2088呎 (4+房)
 $12038万
 $57,653/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38149,7 +38141,7 @@
           <t>B | 1870呎 (4+房)
 $9278万
 $49,617/呎
-(26年-07月-03日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -38164,7 +38156,7 @@
           <t>A | 2088呎 (4+房)
 $10255万
 $49,113/呎
-(23年-02月-02日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38172,7 +38164,7 @@
           <t>B | 1870呎 (4+房)
 $8013万
 $42,850/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -38187,7 +38179,7 @@
           <t>A | 2088呎 (4+房)
 $10110万
 $48,419/呎
-(23年-01月-30日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38195,7 +38187,7 @@
           <t>B | 1816呎 (4+房)
 $9054万
 $49,856/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -38210,7 +38202,7 @@
           <t>A | 2088呎 (4+房)
 $10252万
 $49,100/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38218,7 +38210,7 @@
           <t>B | 1870呎 (4+房)
 $8578万
 $45,870/呎
-(25年-10月-26日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -38233,7 +38225,7 @@
           <t>A | 2088呎 (4+房)
 $10085万
 $48,300/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -38241,7 +38233,7 @@
           <t>B | 1870呎 (4+房)
 $8929万
 $47,748/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38248,7 @@
           <t>A | 2088呎 (4+房)
 $10117万
 $48,453/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -38264,7 +38256,7 @@
           <t>B | 1816呎 (4+房)
 $8690万
 $47,852/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38271,7 @@
           <t>A | 2088呎 (4+房)
 $9855万
 $47,200/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -38287,7 +38279,7 @@
           <t>B | 1870呎 (4+房)
 $8308万
 $44,429/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -38302,7 +38294,7 @@
           <t>A | 2088呎 (4+房)
 $9587万
 $45,913/呎
-(23年-02月-14日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -38310,7 +38302,7 @@
           <t>B | 1870呎 (4+房)
 $8207万
 $43,889/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38317,7 @@
           <t>A | 2088呎 (4+房)
 $9324万
 $44,653/呎
-(23年-01月-30日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -38333,7 +38325,7 @@
           <t>B | 1870呎 (4+房)
 $8477万
 $45,333/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38340,7 @@
           <t>A | 2088呎 (4+房)
 $9542万
 $45,700/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -38356,7 +38348,7 @@
           <t>B | 1870呎 (4+房)
 $7386万
 $39,500/呎
-(24年-06月-06日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -38371,7 +38363,7 @@
           <t>A | 2088呎 (4+房)
 $9420万
 $45,115/呎
-(23年-01月-19日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -38379,7 +38371,7 @@
           <t>B | 1870呎 (4+房)
 $7939万
 $42,457/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -38394,7 +38386,7 @@
           <t>A | 2088呎 (4+房)
 $8403万
 $40,242/呎
-(23年-01月-12日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -38402,7 +38394,7 @@
           <t>B | 1870呎 (4+房)
 $7315万
 $39,120/呎
-(23年-01月-12日)</t>
+(23年-01月)</t>
         </is>
       </c>
     </row>
@@ -38417,7 +38409,7 @@
           <t>A | 2088呎 (4+房)
 $8456万
 $40,500/呎
-(23年-03月-01日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -38425,7 +38417,7 @@
           <t>B | 1870呎 (4+房)
 $7143万
 $38,200/呎
-(23年-03月-01日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -38440,7 +38432,7 @@
           <t>A | 2088呎 (4+房)
 $9271万
 $44,400/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -38448,7 +38440,7 @@
           <t>B | 1870呎 (4+房)
 $8182万
 $43,753/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -38463,7 +38455,7 @@
           <t>A | 2088呎 (4+房)
 $9703万
 $46,472/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -38471,7 +38463,7 @@
           <t>B | 1870呎 (4+房)
 $7750万
 $41,444/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -38486,7 +38478,7 @@
           <t>A | 2088呎 (4+房)
 $9127万
 $43,710/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -38494,7 +38486,7 @@
           <t>B | 1870呎 (4+房)
 $7696万
 $41,157/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -38509,7 +38501,7 @@
           <t>A | 2088呎 (4+房)
 $9427万
 $45,150/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -38517,7 +38509,7 @@
           <t>B | 1870呎 (4+房)
 $7684万
 $41,089/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -38532,7 +38524,7 @@
           <t>A | 1985呎 (4+房)
 $8658万
 $43,617/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -38540,7 +38532,7 @@
           <t>B | 1797呎 (4+房)
 $7178万
 $39,946/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -38781,7 +38773,7 @@
           <t>A | 1909呎 (4+房)
 $9704万
 $50,832/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38789,7 +38781,7 @@
           <t>B | 1870呎 (4+房)
 $9146万
 $48,910/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -38858,7 +38850,7 @@
           <t>B | 1870呎 (4+房)
 $8415万
 $45,000/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -38873,7 +38865,7 @@
           <t>A | 1909呎 (4+房)
 $9434万
 $49,421/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -38896,7 +38888,7 @@
           <t>A | 1909呎 (4+房)
 $9490万
 $49,712/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -38919,7 +38911,7 @@
           <t>A | 1909呎 (4+房)
 $8880万
 $46,517/呎
-(23年-02月-12日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -38942,7 +38934,7 @@
           <t>A | 1909呎 (4+房)
 $9295万
 $48,690/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -38965,7 +38957,7 @@
           <t>A | 1909呎 (4+房)
 $9015万
 $47,221/呎
-(23年-07月-05日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38973,7 +38965,7 @@
           <t>B | 1816呎 (4+房)
 $9086万
 $50,033/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -38988,7 +38980,7 @@
           <t>A | 1909呎 (4+房)
 $9017万
 $47,236/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -39011,7 +39003,7 @@
           <t>A | 1909呎 (4+房)
 $8552万
 $44,800/呎
-(25年-02月-16日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -39019,7 +39011,7 @@
           <t>B | 1870呎 (4+房)
 $8265万
 $44,200/呎
-(25年-02月-16日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -39034,7 +39026,7 @@
           <t>A | 1909呎 (4+房)
 $8837万
 $46,290/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -39057,7 +39049,7 @@
           <t>A | 1909呎 (4+房)
 $8302万
 $43,490/呎
-(24年-09月-10日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -39065,7 +39057,7 @@
           <t>B | 1870呎 (4+房)
 $8103万
 $43,329/呎
-(24年-09月-10日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -39080,7 +39072,7 @@
           <t>A | 1909呎 (4+房)
 $7865万
 $41,200/呎
-(24年-08月-06日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -39088,7 +39080,7 @@
           <t>B | 1870呎 (4+房)
 $7667万
 $41,000/呎
-(24年-08月-06日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -39103,7 +39095,7 @@
           <t>A | 1909呎 (4+房)
 $7770万
 $40,700/呎
-(24年-08月-06日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -39111,7 +39103,7 @@
           <t>B | 1870呎 (4+房)
 $7574万
 $40,500/呎
-(24年-08月-06日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -39126,7 +39118,7 @@
           <t>A | 1909呎 (4+房)
 $8062万
 $42,231/呎
-(24年-07月-21日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -39134,7 +39126,7 @@
           <t>B | 1870呎 (4+房)
 $8054万
 $43,070/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39141,7 @@
           <t>A | 1909呎 (4+房)
 $8319万
 $43,579/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -39157,7 +39149,7 @@
           <t>B | 1870呎 (4+房)
 $7630万
 $40,800/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -39172,7 +39164,7 @@
           <t>A | 1909呎 (4+房)
 $7882万
 $41,290/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39180,7 +39172,7 @@
           <t>B | 1870呎 (4+房)
 $7904万
 $42,270/呎
-(25年-03月-03日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -39195,7 +39187,7 @@
           <t>A | 1909呎 (4+房)
 $7470万
 $39,130/呎
-(23年-07月-05日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39203,7 +39195,7 @@
           <t>B | 1870呎 (4+房)
 $7860万
 $42,029/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -39218,7 +39210,7 @@
           <t>A | 1909呎 (4+房)
 $8131万
 $42,595/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -39226,7 +39218,7 @@
           <t>B | 1870呎 (4+房)
 $7800万
 $41,710/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39241,7 +39233,7 @@
           <t>A | 1909呎 (4+房)
 $8104万
 $42,453/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -39249,7 +39241,7 @@
           <t>B | 1870呎 (4+房)
 $8167万
 $43,673/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -39264,7 +39256,7 @@
           <t>A | 1909呎 (4+房)
 $7708万
 $40,377/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -39272,7 +39264,7 @@
           <t>B | 1870呎 (4+房)
 $7532万
 $40,276/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39287,7 +39279,7 @@
           <t>A | 1909呎 (4+房)
 $7292万
 $38,200/呎
-(24年-06月-19日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -39295,7 +39287,7 @@
           <t>B | 1870呎 (4+房)
 $7704万
 $41,196/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -39310,15 +39302,15 @@
           <t>A | 1909呎 (4+房)
 $7576万
 $39,687/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>B | 1870呎 (4+房)
+          <t>B | 1816呎 (4+房)
 $7996万
-$42,757/呎
-(26年-05月-11日)</t>
+$44,028/呎
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -39333,7 +39325,7 @@
           <t>A | 1828呎 (4+房)
 $7534万
 $41,213/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -39341,7 +39333,7 @@
           <t>B | 1797呎 (4+房)
 $7380万
 $41,069/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39409,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39427,7 +39419,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39479,7 +39471,7 @@
           <t>A | 1129呎 (3房)
 $5215万
 $46,195/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -39487,7 +39479,7 @@
           <t>B | 1334呎 (3房)
 $3869万
 $29,000/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr"/>
@@ -39504,7 +39496,7 @@
           <t>A | 577呎 (2房)
 $1546万
 $26,800/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -39512,7 +39504,7 @@
           <t>B | 554呎 (2房)
 $1391万
 $25,100/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -39543,7 +39535,7 @@
           <t>A | 577呎 (2房)
 $1512万
 $26,200/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -39551,7 +39543,7 @@
           <t>B | 553呎 (2房)
 $1363万
 $24,644/呎
-(26年-06月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -39621,7 +39613,7 @@
           <t>A | 577呎 (2房)
 $1489万
 $25,810/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -39629,7 +39621,7 @@
           <t>B | 554呎 (2房)
 $1324万
 $23,900/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39660,15 +39652,15 @@
           <t>A | 577呎 (2房)
 $1482万
 $25,681/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1319万
-$23,800/呎
-(26年-06月-10日)</t>
+$23,843/呎
+(26年-06月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39699,15 +39691,15 @@
           <t>A | 577呎 (2房)
 $1474万
 $25,554/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1341万
-$24,200/呎
-(26年-06月-11日)</t>
+$24,244/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -39738,15 +39730,15 @@
           <t>A | 577呎 (2房)
 $1467万
 $25,426/呎
-(25年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
-招标单位
--
-(在售)</t>
+$1335万
+$24,100/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -39777,7 +39769,7 @@
           <t>A | 577呎 (2房)
 $1460万
 $25,300/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39785,7 +39777,7 @@
           <t>B | 554呎 (2房)
 $1319万
 $23,800/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39816,7 +39808,7 @@
           <t>A | 577呎 (2房)
 $1469万
 $25,454/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39824,7 +39816,7 @@
           <t>B | 554呎 (2房)
 $1285万
 $23,200/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -39832,7 +39824,7 @@
           <t>C | 509呎 (2房)
 $1196万
 $23,500/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -39855,7 +39847,7 @@
           <t>A | 577呎 (2房)
 $1438万
 $24,925/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39863,7 +39855,7 @@
           <t>B | 554呎 (2房)
 $1274万
 $23,000/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -39871,7 +39863,7 @@
           <t>C | 509呎 (2房)
 $1191万
 $23,400/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -39894,7 +39886,7 @@
           <t>A | 577呎 (2房)
 $1431万
 $24,801/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39902,7 +39894,7 @@
           <t>B | 554呎 (2房)
 $1269万
 $22,900/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -39910,7 +39902,7 @@
           <t>C | 509呎 (2房)
 $1186万
 $23,300/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -39933,7 +39925,7 @@
           <t>A | 577呎 (2房)
 $1424万
 $24,677/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -39941,7 +39933,7 @@
           <t>B | 553呎 (2房)
 $1302万
 $23,542/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39972,7 +39964,7 @@
           <t>A | 577呎 (2房)
 $1417万
 $24,555/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -39980,7 +39972,7 @@
           <t>B | 554呎 (2房)
 $1280万
 $23,100/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -40011,7 +40003,7 @@
           <t>A | 577呎 (2房)
 $1410万
 $24,432/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -40019,7 +40011,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40050,7 +40042,7 @@
           <t>A | 577呎 (2房)
 $1403万
 $24,311/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40058,7 +40050,7 @@
           <t>B | 553呎 (2房)
 $1285万
 $23,242/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40089,7 +40081,7 @@
           <t>A | 577呎 (2房)
 $1411万
 $24,459/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -40097,7 +40089,7 @@
           <t>B | 554呎 (2房)
 $1280万
 $23,100/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -40128,15 +40120,15 @@
           <t>A | 577呎 (2房)
 $1389万
 $24,070/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1274万
-$23,000/呎
-(26年-06月-22日)</t>
+$23,042/呎
+(26年-06月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40167,7 +40159,7 @@
           <t>A | 577呎 (2房)
 $1382万
 $23,950/呎
-(24年-12月-30日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40175,7 +40167,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40206,7 +40198,7 @@
           <t>A | 577呎 (2房)
 $1368万
 $23,713/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40214,7 +40206,7 @@
           <t>B | 554呎 (2房)
 $1258万
 $22,700/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -40222,7 +40214,7 @@
           <t>C | 509呎 (2房)
 $1155万
 $22,700/呎
-(26年-06月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -40245,15 +40237,15 @@
           <t>A | 577呎 (2房)
 $1361万
 $23,595/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1252万
-$22,600/呎
-(26年-06月-03日)</t>
+$22,641/呎
+(26年-06月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -40261,7 +40253,7 @@
           <t>C | 509呎 (2房)
 $1150万
 $22,600/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -40284,7 +40276,7 @@
           <t>A | 577呎 (2房)
 $1355万
 $23,477/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40292,7 +40284,7 @@
           <t>B | 554呎 (2房)
 $1295万
 $23,377/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -40323,7 +40315,7 @@
           <t>A | 577呎 (2房)
 $1348万
 $23,361/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40331,7 +40323,7 @@
           <t>B | 553呎 (2房)
 $1252万
 $22,641/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40362,7 +40354,7 @@
           <t>A | 577呎 (2房)
 $1341万
 $23,244/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40370,7 +40362,7 @@
           <t>B | 554呎 (2房)
 $1246万
 $22,500/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40401,7 +40393,7 @@
           <t>A | 577呎 (2房)
 $1335万
 $23,129/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -40409,7 +40401,7 @@
           <t>B | 554呎 (2房)
 $1235万
 $22,300/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40440,7 +40432,7 @@
           <t>A | 577呎 (2房)
 $1247万
 $21,606/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40479,7 +40471,7 @@
           <t>A | 577呎 (2房)
 $1210万
 $20,976/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40518,7 +40510,7 @@
           <t>A | 577呎 (2房)
 $1198万
 $20,769/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40557,7 +40549,7 @@
           <t>A | 577呎 (2房)
 $1195万
 $20,706/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -40596,7 +40588,7 @@
           <t>A | 577呎 (2房)
 $1191万
 $20,644/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -40635,7 +40627,7 @@
           <t>A | 539呎 (2房)
 $1197万
 $22,200/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -40808,7 +40800,7 @@
           <t>A | 659呎 (2房)
 $1799万
 $27,300/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -40816,7 +40808,7 @@
           <t>B | 523呎 (2房)
 $1423万
 $27,200/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -40824,7 +40816,7 @@
           <t>C | 568呎 (2房)
 $1551万
 $27,300/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -40839,7 +40831,7 @@
           <t>A | 659呎 (2房)
 $1766万
 $26,800/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -40847,7 +40839,7 @@
           <t>B | 523呎 (2房)
 $1396万
 $26,700/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -40855,7 +40847,7 @@
           <t>C | 568呎 (2房)
 $1522万
 $26,800/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -40870,7 +40862,7 @@
           <t>A | 659呎 (2房)
 $1746万
 $26,500/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -40878,7 +40870,7 @@
           <t>B | 523呎 (2房)
 $1381万
 $26,400/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -40886,7 +40878,7 @@
           <t>C | 568呎 (2房)
 $1505万
 $26,500/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -40901,7 +40893,7 @@
           <t>A | 659呎 (2房)
 $1735万
 $26,323/呎
-(25年-03月-11日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -40909,7 +40901,7 @@
           <t>B | 523呎 (2房)
 $1371万
 $26,205/呎
-(24年-07月-16日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -40917,7 +40909,7 @@
           <t>C | 1644呎 (2房)
 $1496万
 $9,099/呎
-(24年-06月-16日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -40932,7 +40924,7 @@
           <t>A | 659呎 (2房)
 $1726万
 $26,192/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -40940,7 +40932,7 @@
           <t>B | 523呎 (2房)
 $1364万
 $26,075/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -40948,7 +40940,7 @@
           <t>C | 568呎 (2房)
 $1488万
 $26,205/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40963,7 +40955,7 @@
           <t>A | 659呎 (2房)
 $1717万
 $26,062/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -40971,7 +40963,7 @@
           <t>B | 523呎 (2房)
 $1357万
 $25,945/呎
-(25年-07月-27日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -40979,7 +40971,7 @@
           <t>C | 568呎 (2房)
 $1481万
 $26,075/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -40994,7 +40986,7 @@
           <t>A | 659呎 (2房)
 $1709万
 $25,932/呎
-(25年-06月-02日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -41002,7 +40994,7 @@
           <t>B | 523呎 (2房)
 $1350万
 $25,816/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41010,7 +41002,7 @@
           <t>C | 568呎 (2房)
 $1474万
 $25,945/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41025,7 +41017,7 @@
           <t>A | 659呎 (2房)
 $1700万
 $25,803/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -41033,7 +41025,7 @@
           <t>B | 523呎 (2房)
 $1343万
 $25,688/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41041,7 +41033,7 @@
           <t>C | 568呎 (2房)
 $1466万
 $25,816/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41048,7 @@
           <t>A | 659呎 (2房)
 $1692万
 $25,675/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -41064,7 +41056,7 @@
           <t>B | 523呎 (2房)
 $1337万
 $25,560/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41072,7 +41064,7 @@
           <t>C | 568呎 (2房)
 $1459万
 $25,688/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41087,7 +41079,7 @@
           <t>A | 659呎 (2房)
 $1675万
 $25,421/呎
-(25年-02月-27日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -41095,7 +41087,7 @@
           <t>B | 523呎 (2房)
 $1324万
 $25,307/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41103,7 +41095,7 @@
           <t>C | 568呎 (2房)
 $1445万
 $25,433/呎
-(24年-06月-13日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -41118,7 +41110,7 @@
           <t>A | 659呎 (2房)
 $1667万
 $25,294/呎
-(24年-06月-06日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -41126,7 +41118,7 @@
           <t>B | 523呎 (2房)
 $1317万
 $25,181/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41134,7 +41126,7 @@
           <t>C | 568呎 (2房)
 $1437万
 $25,307/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -41149,7 +41141,7 @@
           <t>A | 659呎 (2房)
 $1659万
 $25,168/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -41157,7 +41149,7 @@
           <t>B | 523呎 (2房)
 $1310万
 $25,056/呎
-(24年-09月-16日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41165,7 +41157,7 @@
           <t>C | 568呎 (2房)
 $1430万
 $25,181/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41180,7 +41172,7 @@
           <t>A | 659呎 (2房)
 $1650万
 $25,043/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -41188,7 +41180,7 @@
           <t>B | 523呎 (2房)
 $1304万
 $24,931/呎
-(24年-09月-16日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41196,7 +41188,7 @@
           <t>C | 568呎 (2房)
 $1423万
 $25,056/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41211,7 +41203,7 @@
           <t>A | 659呎 (2房)
 $1642万
 $24,919/呎
-(24年-08月-05日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -41219,7 +41211,7 @@
           <t>B | 523呎 (2房)
 $1297万
 $24,807/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41227,7 +41219,7 @@
           <t>C | 568呎 (2房)
 $1416万
 $24,931/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41242,7 +41234,7 @@
           <t>A | 659呎 (2房)
 $1634万
 $24,795/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -41250,7 +41242,7 @@
           <t>B | 523呎 (2房)
 $1291万
 $24,684/呎
-(24年-07月-30日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41258,7 +41250,7 @@
           <t>C | 568呎 (2房)
 $1409万
 $24,807/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41273,7 +41265,7 @@
           <t>A | 656呎 (2房)
 $1618万
 $24,671/呎
-(24年-07月-16日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -41281,7 +41273,7 @@
           <t>B | 526呎 (2房)
 $1292万
 $24,561/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41289,7 +41281,7 @@
           <t>C | 568呎 (2房)
 $1402万
 $24,684/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41296,7 @@
           <t>A | 656呎 (2房)
 $1610万
 $24,549/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -41312,7 +41304,7 @@
           <t>B | 526呎 (2房)
 $1285万
 $24,439/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41320,7 +41312,7 @@
           <t>C | 568呎 (2房)
 $1395万
 $24,561/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41335,7 +41327,7 @@
           <t>A | 656呎 (2房)
 $1602万
 $24,427/呎
-(24年-05月-12日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -41343,7 +41335,7 @@
           <t>B | 526呎 (2房)
 $1279万
 $24,317/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41351,7 +41343,7 @@
           <t>C | 568呎 (2房)
 $1388万
 $24,439/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41366,7 +41358,7 @@
           <t>A | 656呎 (2房)
 $1587万
 $24,185/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -41374,7 +41366,7 @@
           <t>B | 526呎 (2房)
 $1266万
 $24,076/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41382,7 +41374,7 @@
           <t>C | 568呎 (2房)
 $1374万
 $24,197/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41397,7 +41389,7 @@
           <t>A | 656呎 (2房)
 $1579万
 $24,064/呎
-(24年-07月-28日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -41405,7 +41397,7 @@
           <t>B | 526呎 (2房)
 $1260万
 $23,956/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41413,7 +41405,7 @@
           <t>C | 568呎 (2房)
 $1368万
 $24,076/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41428,7 +41420,7 @@
           <t>A | 656呎 (2房)
 $1571万
 $23,945/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -41436,7 +41428,7 @@
           <t>B | 526呎 (2房)
 $1254万
 $23,837/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41444,7 +41436,7 @@
           <t>C | 568呎 (2房)
 $1376万
 $24,223/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41459,7 +41451,7 @@
           <t>A | 656呎 (2房)
 $1563万
 $23,825/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -41467,7 +41459,7 @@
           <t>B | 526呎 (2房)
 $1248万
 $23,719/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41475,7 +41467,7 @@
           <t>C | 568呎 (2房)
 $1354万
 $23,837/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41490,7 +41482,7 @@
           <t>A | 656呎 (2房)
 $1555万
 $23,707/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -41498,7 +41490,7 @@
           <t>B | 526呎 (2房)
 $1241万
 $23,601/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41506,7 +41498,7 @@
           <t>C | 568呎 (2房)
 $1347万
 $23,719/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41521,7 +41513,7 @@
           <t>A | 656呎 (2房)
 $1547万
 $23,589/呎
-(25年-03月-03日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -41529,7 +41521,7 @@
           <t>B | 526呎 (2房)
 $1235万
 $23,483/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -41537,7 +41529,7 @@
           <t>C | 568呎 (2房)
 $1355万
 $23,863/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41552,7 +41544,7 @@
           <t>A | 656呎 (2房)
 $1429万
 $21,790/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -41560,7 +41552,7 @@
           <t>B | 526呎 (2房)
 $1158万
 $22,014/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -41568,7 +41560,7 @@
           <t>C | 568呎 (2房)
 $1250万
 $22,014/呎
-(25年-04月-06日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -41583,7 +41575,7 @@
           <t>A | 656呎 (2房)
 $1361万
 $20,752/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -41591,7 +41583,7 @@
           <t>B | 526呎 (2房)
 $1103万
 $20,966/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -41599,7 +41591,7 @@
           <t>C | 568呎 (2房)
 $1191万
 $20,966/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -41614,7 +41606,7 @@
           <t>A | 656呎 (2房)
 $1335万
 $20,345/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -41622,7 +41614,7 @@
           <t>B | 526呎 (2房)
 $1081万
 $20,555/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -41630,7 +41622,7 @@
           <t>C | 568呎 (2房)
 $1179万
 $20,758/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -41645,7 +41637,7 @@
           <t>A | 656呎 (2房)
 $1331万
 $20,284/呎
-(25年-04月-06日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -41653,7 +41645,7 @@
           <t>B | 526呎 (2房)
 $1078万
 $20,493/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -41661,7 +41653,7 @@
           <t>C | 568呎 (2房)
 $1176万
 $20,696/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41668,7 @@
           <t>A | 656呎 (2房)
 $1327万
 $20,223/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -41684,7 +41676,7 @@
           <t>B | 526呎 (2房)
 $1075万
 $20,432/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -41692,7 +41684,7 @@
           <t>C | 568呎 (2房)
 $1172万
 $20,634/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -41707,7 +41699,7 @@
           <t>A | 618呎 (2房)
 $1259万
 $20,371/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -41715,7 +41707,7 @@
           <t>B | 488呎 (2房)
 $1014万
 $20,787/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -41723,7 +41715,7 @@
           <t>C | 530呎 (2房)
 $1166万
 $22,000/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -41872,7 +41864,7 @@
           <t>A | 903呎 (3房)
 $3070万
 $33,998/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -41880,7 +41872,7 @@
           <t>B | 564呎 (2房)
 $1884万
 $33,400/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -41888,7 +41880,7 @@
           <t>C | 620呎 (2房)
 $1978万
 $31,900/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -41903,7 +41895,7 @@
           <t>A | 903呎 (3房)
 $3043万
 $33,700/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -41911,7 +41903,7 @@
           <t>B | 564呎 (2房)
 $1844万
 $32,700/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -41919,7 +41911,7 @@
           <t>C | 620呎 (2房)
 $1941万
 $31,300/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -41934,7 +41926,7 @@
           <t>A | 900呎 (3房)
 $3043万
 $33,812/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -41942,7 +41934,7 @@
           <t>B | 564呎 (2房)
 $1827万
 $32,400/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -41950,7 +41942,7 @@
           <t>C | 620呎 (2房)
 $1916万
 $30,900/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41957,7 @@
           <t>A | 903呎 (3房)
 $2935万
 $32,500/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -41973,7 +41965,7 @@
           <t>B | 564呎 (2房)
 $1816万
 $32,200/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -41981,7 +41973,7 @@
           <t>C | 620呎 (2房)
 $1904万
 $30,712/呎
-(25年-06月-01日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -41996,7 +41988,7 @@
           <t>A | 903呎 (3房)
 $2946万
 $32,623/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -42004,7 +41996,7 @@
           <t>B | 564呎 (2房)
 $1805万
 $32,000/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -42012,7 +42004,7 @@
           <t>C | 620呎 (2房)
 $1914万
 $30,868/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -42027,7 +42019,7 @@
           <t>A | 903呎 (3房)
 $2899万
 $32,100/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -42035,7 +42027,7 @@
           <t>B | 564呎 (2房)
 $1794万
 $31,800/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -42043,7 +42035,7 @@
           <t>C | 620呎 (2房)
 $1902万
 $30,684/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -42058,7 +42050,7 @@
           <t>A | 903呎 (3房)
 $2935万
 $32,500/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -42066,7 +42058,7 @@
           <t>B | 564呎 (2房)
 $1782万
 $31,600/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -42074,7 +42066,7 @@
           <t>C | 620呎 (2房)
 $1870万
 $30,165/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -42089,7 +42081,7 @@
           <t>A | 903呎 (3房)
 $2862万
 $31,700/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -42097,7 +42089,7 @@
           <t>B | 564呎 (2房)
 $1771万
 $31,400/呎
-(25年-08月-06日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -42105,7 +42097,7 @@
           <t>C | 620呎 (2房)
 $1859万
 $29,985/呎
-(24年-09月-16日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -42120,7 +42112,7 @@
           <t>A | 903呎 (3房)
 $2872万
 $31,805/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -42128,7 +42120,7 @@
           <t>B | 564呎 (2房)
 $1760万
 $31,200/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -42136,7 +42128,7 @@
           <t>C | 620呎 (2房)
 $1848万
 $29,807/呎
-(24年-06月-16日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -42151,7 +42143,7 @@
           <t>A | 903呎 (3房)
 $2946万
 $32,630/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -42159,7 +42151,7 @@
           <t>B | 564呎 (2房)
 $1779万
 $31,534/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -42167,7 +42159,7 @@
           <t>C | 620呎 (2房)
 $1828万
 $29,482/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -42182,7 +42174,7 @@
           <t>A | 903呎 (3房)
 $3180万
 $35,217/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -42190,7 +42182,7 @@
           <t>B | 564呎 (2房)
 $1687万
 $29,917/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -42198,7 +42190,7 @@
           <t>C | 620呎 (2房)
 $1781万
 $28,732/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42205,7 @@
           <t>A | 903呎 (3房)
 $2781万
 $30,800/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -42221,7 +42213,7 @@
           <t>B | 564呎 (2房)
 $1719万
 $30,482/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -42229,7 +42221,7 @@
           <t>C | 620呎 (2房)
 $1790万
 $28,878/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42244,7 +42236,7 @@
           <t>A | 903呎 (3房)
 $2798万
 $30,982/呎
-(24年-03月-18日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -42252,7 +42244,7 @@
           <t>B | 564呎 (2房)
 $1709万
 $30,300/呎
-(24年-08月-13日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -42260,7 +42252,7 @@
           <t>C | 620呎 (2房)
 $1780万
 $28,706/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42275,7 +42267,7 @@
           <t>A | 903呎 (3房)
 $2745万
 $30,400/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -42283,7 +42275,7 @@
           <t>B | 564呎 (2房)
 $1699万
 $30,119/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -42291,7 +42283,7 @@
           <t>C | 620呎 (2房)
 $1769万
 $28,534/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42306,7 +42298,7 @@
           <t>A | 903呎 (3房)
 $2764万
 $30,604/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -42314,7 +42306,7 @@
           <t>B | 564呎 (2房)
 $1689万
 $29,939/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -42322,7 +42314,7 @@
           <t>C | 620呎 (2房)
 $1759万
 $28,364/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42337,7 +42329,7 @@
           <t>A | 902呎 (3房)
 $2867万
 $31,785/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -42345,7 +42337,7 @@
           <t>B | 567呎 (2房)
 $1725万
 $30,422/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -42353,7 +42345,7 @@
           <t>C | 619呎 (2房)
 $1726万
 $27,885/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42368,7 +42360,7 @@
           <t>A | 902呎 (3房)
 $2697万
 $29,900/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -42376,7 +42368,7 @@
           <t>B | 567呎 (2房)
 $1677万
 $29,583/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -42384,7 +42376,7 @@
           <t>C | 619呎 (2房)
 $1716万
 $27,719/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42399,7 +42391,7 @@
           <t>A | 902呎 (3房)
 $2679万
 $29,700/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -42407,7 +42399,7 @@
           <t>B | 567呎 (2房)
 $1667万
 $29,407/呎
-(24年-08月-19日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -42415,7 +42407,7 @@
           <t>C | 619呎 (2房)
 $1725万
 $27,860/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42430,7 +42422,7 @@
           <t>A | 902呎 (3房)
 $2661万
 $29,500/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -42438,7 +42430,7 @@
           <t>B | 567呎 (2房)
 $1627万
 $28,693/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -42446,7 +42438,7 @@
           <t>C | 619呎 (2房)
 $1706万
 $27,557/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42461,7 +42453,7 @@
           <t>A | 902呎 (3房)
 $2634万
 $29,200/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -42469,7 +42461,7 @@
           <t>B | 567呎 (2房)
 $1617万
 $28,522/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -42477,7 +42469,7 @@
           <t>C | 619呎 (2房)
 $1677万
 $27,091/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42492,7 +42484,7 @@
           <t>A | 902呎 (3房)
 $2713万
 $30,082/呎
-(23年-10月-19日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -42500,7 +42492,7 @@
           <t>B | 567呎 (2房)
 $1590万
 $28,040/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -42508,7 +42500,7 @@
           <t>C | 619呎 (2房)
 $1700万
 $27,468/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -42523,7 +42515,7 @@
           <t>A | 902呎 (3房)
 $2970万
 $32,924/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -42531,7 +42523,7 @@
           <t>B | 567呎 (2房)
 $1598万
 $28,183/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -42539,7 +42531,7 @@
           <t>C | 619呎 (2房)
 $1657万
 $26,769/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42554,7 +42546,7 @@
           <t>A | 902呎 (3房)
 $2589万
 $28,700/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -42562,7 +42554,7 @@
           <t>B | 567呎 (2房)
 $1588万
 $28,014/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -42570,7 +42562,7 @@
           <t>C | 619呎 (2房)
 $1647万
 $26,609/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42585,7 +42577,7 @@
           <t>A | 902呎 (3房)
 $2571万
 $28,500/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -42593,7 +42585,7 @@
           <t>B | 567呎 (2房)
 $1562万
 $27,541/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -42601,7 +42593,7 @@
           <t>C | 619呎 (2房)
 $1637万
 $26,451/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42616,7 +42608,7 @@
           <t>A | 902呎 (3房)
 $2526万
 $28,000/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -42624,7 +42616,7 @@
           <t>B | 567呎 (2房)
 $1442万
 $25,438/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -42632,7 +42624,7 @@
           <t>C | 619呎 (2房)
 $1530万
 $24,714/呎
-(25年-03月-11日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -42647,7 +42639,7 @@
           <t>A | 902呎 (3房)
 $2089万
 $23,156/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -42655,7 +42647,7 @@
           <t>B | 567呎 (2房)
 $1299万
 $22,917/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -42663,7 +42655,7 @@
           <t>C | 619呎 (2房)
 $1391万
 $22,468/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -42678,7 +42670,7 @@
           <t>A | 902呎 (3房)
 $1989万
 $22,053/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -42686,7 +42678,7 @@
           <t>B | 567呎 (2房)
 $1238万
 $21,826/呎
-(25年-03月-11日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -42694,7 +42686,7 @@
           <t>C | 619呎 (2房)
 $1337万
 $21,604/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -42709,7 +42701,7 @@
           <t>A | 902呎 (3房)
 $1983万
 $21,987/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -42717,7 +42709,7 @@
           <t>B | 567呎 (2房)
 $1234万
 $21,760/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -42725,7 +42717,7 @@
           <t>C | 619呎 (2房)
 $1333万
 $21,539/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -42740,7 +42732,7 @@
           <t>A | 902呎 (3房)
 $1977万
 $21,921/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -42748,7 +42740,7 @@
           <t>B | 567呎 (2房)
 $1230万
 $21,695/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -42756,7 +42748,7 @@
           <t>C | 619呎 (2房)
 $1329万
 $21,474/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -42771,7 +42763,7 @@
           <t>A | 869呎 (3房)
 $1921万
 $22,106/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -42779,7 +42771,7 @@
           <t>B | 529呎 (2房)
 $1165万
 $22,027/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -42787,7 +42779,7 @@
           <t>C | 597呎 (2房)
 $1292万
 $21,644/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -42936,7 +42928,7 @@
           <t>A | 950呎 (3房)
 $3515万
 $37,000/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -42944,7 +42936,7 @@
           <t>B | 781呎 (3房)
 $2761万
 $35,350/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -42952,7 +42944,7 @@
           <t>C | 903呎 (3房)
 $3133万
 $34,700/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42967,7 +42959,7 @@
           <t>A | 950呎 (3房)
 $3397万
 $35,754/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -42975,7 +42967,7 @@
           <t>B | 781呎 (3房)
 $2706万
 $34,643/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -42983,7 +42975,7 @@
           <t>C | 903呎 (3房)
 $3101万
 $34,340/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42998,7 +42990,7 @@
           <t>A | 950呎 (3房)
 $3473万
 $36,554/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -43006,7 +42998,7 @@
           <t>B | 781呎 (3房)
 $2773万
 $35,510/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -43014,7 +43006,7 @@
           <t>C | 903呎 (3房)
 $3043万
 $33,700/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43029,7 +43021,7 @@
           <t>A | 950呎 (3房)
 $3914万
 $41,198/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -43037,7 +43029,7 @@
           <t>B | 781呎 (3房)
 $2666万
 $34,138/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -43045,7 +43037,7 @@
           <t>C | 903呎 (3房)
 $3025万
 $33,500/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43060,7 +43052,7 @@
           <t>A | 950呎 (3房)
 $3539万
 $37,254/呎
-(23年-03月-05日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -43068,7 +43060,7 @@
           <t>B | 781呎 (3房)
 $2646万
 $33,880/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -43076,7 +43068,7 @@
           <t>C | 903呎 (3房)
 $3010万
 $33,330/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43091,7 +43083,7 @@
           <t>A | 950呎 (3房)
 $3711万
 $39,061/呎
-(23年-03月-05日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -43099,7 +43091,7 @@
           <t>B | 781呎 (3房)
 $2609万
 $33,400/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -43107,7 +43099,7 @@
           <t>C | 903呎 (3房)
 $2989万
 $33,100/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43122,7 +43114,7 @@
           <t>A | 950呎 (3房)
 $3671万
 $38,638/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -43130,7 +43122,7 @@
           <t>B | 781呎 (3房)
 $2708万
 $34,674/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -43138,7 +43130,7 @@
           <t>C | 903呎 (3房)
 $3340万
 $36,992/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43153,7 +43145,7 @@
           <t>A | 950呎 (3房)
 $3223万
 $33,928/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -43161,7 +43153,7 @@
           <t>B | 781呎 (3房)
 $2708万
 $34,677/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -43169,7 +43161,7 @@
           <t>C | 903呎 (3房)
 $2953万
 $32,700/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43184,7 +43176,7 @@
           <t>A | 950呎 (3房)
 $3211万
 $33,800/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -43192,7 +43184,7 @@
           <t>B | 781呎 (3房)
 $2562万
 $32,800/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -43200,7 +43192,7 @@
           <t>C | 903呎 (3房)
 $3046万
 $33,734/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43215,7 +43207,7 @@
           <t>A | 950呎 (3房)
 $3618万
 $38,084/呎
-(23年-02月-01日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -43223,7 +43215,7 @@
           <t>B | 781呎 (3房)
 $2530万
 $32,399/呎
-(23年-05月-24日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -43231,7 +43223,7 @@
           <t>C | 903呎 (3房)
 $2888万
 $31,977/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43246,7 +43238,7 @@
           <t>A | 950呎 (3房)
 $3154万
 $33,200/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -43254,7 +43246,7 @@
           <t>B | 781呎 (3房)
 $2550万
 $32,650/呎
-(23年-03月-13日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -43262,7 +43254,7 @@
           <t>C | 903呎 (3房)
 $2938万
 $32,538/呎
-(23年-05月-18日)</t>
+(23年-05月)</t>
         </is>
       </c>
     </row>
@@ -43277,7 +43269,7 @@
           <t>A | 950呎 (3房)
 $3480万
 $36,628/呎
-(22年-12月-12日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -43285,7 +43277,7 @@
           <t>B | 781呎 (3房)
 $2534万
 $32,445/呎
-(23年-03月-06日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -43293,7 +43285,7 @@
           <t>C | 903呎 (3房)
 $3217万
 $35,626/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -43308,7 +43300,7 @@
           <t>A | 950呎 (3房)
 $3221万
 $33,902/呎
-(23年-02月-01日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -43316,7 +43308,7 @@
           <t>B | 781呎 (3房)
 $2491万
 $31,900/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -43324,7 +43316,7 @@
           <t>C | 903呎 (3房)
 $2936万
 $32,514/呎
-(23年-04月-12日)</t>
+(23年-04月)</t>
         </is>
       </c>
     </row>
@@ -43339,7 +43331,7 @@
           <t>A | 950呎 (3房)
 $3200万
 $33,687/呎
-(23年-02月-01日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -43347,7 +43339,7 @@
           <t>B | 781呎 (3房)
 $2476万
 $31,700/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -43355,7 +43347,7 @@
           <t>C | 903呎 (3房)
 $2835万
 $31,400/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -43370,7 +43362,7 @@
           <t>A | 950呎 (3房)
 $3564万
 $37,513/呎
-(23年-01月-12日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -43378,7 +43370,7 @@
           <t>B | 781呎 (3房)
 $2460万
 $31,500/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -43386,7 +43378,7 @@
           <t>C | 903呎 (3房)
 $2817万
 $31,200/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -43401,7 +43393,7 @@
           <t>A | 948呎 (3房)
 $3334万
 $35,165/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -43409,7 +43401,7 @@
           <t>B | 784呎 (3房)
 $2980万
 $38,010/呎
-(22年-12月-27日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -43417,7 +43409,7 @@
           <t>C | 902呎 (3房)
 $2742万
 $30,399/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -43432,7 +43424,7 @@
           <t>A | 948呎 (3房)
 $3268万
 $34,473/呎
-(22年-12月-12日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -43440,7 +43432,7 @@
           <t>B | 784呎 (3房)
 $2465万
 $31,444/呎
-(23年-02月-08日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -43448,7 +43440,7 @@
           <t>C | 902呎 (3房)
 $3120万
 $34,591/呎
-(23年-02月-08日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -43463,7 +43455,7 @@
           <t>A | 948呎 (3房)
 $3181万
 $33,555/呎
-(23年-02月-09日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -43471,7 +43463,7 @@
           <t>B | 784呎 (3房)
 $2446万
 $31,200/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -43479,7 +43471,7 @@
           <t>C | 902呎 (3房)
 $3028万
 $33,568/呎
-(23年-02月-27日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -43494,7 +43486,7 @@
           <t>A | 948呎 (3房)
 $3002万
 $31,667/呎
-(23年-02月-06日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -43502,7 +43494,7 @@
           <t>B | 784呎 (3房)
 $2447万
 $31,211/呎
-(23年-04月-16日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -43510,7 +43502,7 @@
           <t>C | 902呎 (3房)
 $2760万
 $30,599/呎
-(22年-12月-21日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -43525,7 +43517,7 @@
           <t>A | 948呎 (3房)
 $2967万
 $31,300/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -43533,7 +43525,7 @@
           <t>B | 784呎 (3房)
 $2564万
 $32,702/呎
-(23年-04月-02日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -43541,7 +43533,7 @@
           <t>C | 902呎 (3房)
 $2756万
 $30,550/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -43556,7 +43548,7 @@
           <t>A | 948呎 (3房)
 $2948万
 $31,100/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -43564,7 +43556,7 @@
           <t>B | 784呎 (3房)
 $2376万
 $30,300/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -43572,7 +43564,7 @@
           <t>C | 902呎 (3房)
 $3070万
 $34,034/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -43587,7 +43579,7 @@
           <t>A | 948呎 (3房)
 $2959万
 $31,209/呎
-(23年-02月-05日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -43595,7 +43587,7 @@
           <t>B | 784呎 (3房)
 $2670万
 $34,051/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -43603,7 +43595,7 @@
           <t>C | 902呎 (3房)
 $2733万
 $30,300/呎
-(23年-05月-31日)</t>
+(23年-05月)</t>
         </is>
       </c>
     </row>
@@ -43618,7 +43610,7 @@
           <t>A | 948呎 (3房)
 $2920万
 $30,800/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -43626,7 +43618,7 @@
           <t>B | 784呎 (3房)
 $2344万
 $29,900/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -43634,7 +43626,7 @@
           <t>C | 902呎 (3房)
 $2670万
 $29,600/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43641,7 @@
           <t>A | 948呎 (3房)
 $3151万
 $33,235/呎
-(24年-03月-12日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -43657,7 +43649,7 @@
           <t>B | 784呎 (3房)
 $2398万
 $30,590/呎
-(24年-01月-16日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -43665,7 +43657,7 @@
           <t>C | 902呎 (3房)
 $2670万
 $29,596/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43680,7 +43672,7 @@
           <t>A | 948呎 (3房)
 $2702万
 $28,500/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -43688,7 +43680,7 @@
           <t>B | 784呎 (3房)
 $2242万
 $28,600/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -43696,7 +43688,7 @@
           <t>C | 902呎 (3房)
 $2598万
 $28,800/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43703,7 @@
           <t>A | 948呎 (3房)
 $2291万
 $24,163/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -43719,7 +43711,7 @@
           <t>B | 784呎 (3房)
 $1850万
 $23,596/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -43727,7 +43719,7 @@
           <t>C | 902呎 (3房)
 $2152万
 $23,856/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -43742,7 +43734,7 @@
           <t>A | 948呎 (3房)
 $2141万
 $22,582/呎
-(25年-04月-15日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -43750,7 +43742,7 @@
           <t>B | 784呎 (3房)
 $1745万
 $22,260/呎
-(25年-04月-15日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -43758,7 +43750,7 @@
           <t>C | 902呎 (3房)
 $2030万
 $22,506/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43765,7 @@
           <t>A | 948呎 (3房)
 $2130万
 $22,469/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -43781,7 +43773,7 @@
           <t>B | 784呎 (3房)
 $1740万
 $22,194/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -43789,7 +43781,7 @@
           <t>C | 902呎 (3房)
 $2024万
 $22,438/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -43804,7 +43796,7 @@
           <t>A | 948呎 (3房)
 $2119万
 $22,357/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -43812,7 +43804,7 @@
           <t>B | 784呎 (3房)
 $1735万
 $22,127/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -43820,7 +43812,7 @@
           <t>C | 902呎 (3房)
 $2018万
 $22,371/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -43835,7 +43827,7 @@
           <t>A | 915呎 (3房)
 $2060万
 $22,518/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -43843,7 +43835,7 @@
           <t>B | 738呎 (3房)
 $1680万
 $22,764/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -43851,7 +43843,7 @@
           <t>C | 869呎 (3房)
 $1960万
 $22,560/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -43977,7 +43969,7 @@
           <t>A | 2729呎 (4+房)
 $16224万
 $59,449/呎
-(23年-09月-27日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
@@ -43993,7 +43985,7 @@
           <t>A | 1523呎 (3房)
 $6543万
 $42,959/呎
-(24年-12月-29日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -44001,7 +43993,7 @@
           <t>B | 1187呎 (3房)
 $4953万
 $41,725/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44016,7 +44008,7 @@
           <t>A | 1523呎 (3房)
 $5742万
 $37,700/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -44024,7 +44016,7 @@
           <t>B | 1187呎 (3房)
 $4522万
 $38,100/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44039,7 +44031,7 @@
           <t>A | 1523呎 (3房)
 $5966万
 $39,174/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -44047,7 +44039,7 @@
           <t>B | 1187呎 (3房)
 $5074万
 $42,743/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44062,7 +44054,7 @@
           <t>A | 1523呎 (3房)
 $5528万
 $36,300/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -44070,7 +44062,7 @@
           <t>B | 1187呎 (3房)
 $4439万
 $37,400/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -44085,7 +44077,7 @@
           <t>A | 1523呎 (3房)
 $5498万
 $36,100/呎
-(24年-12月-17日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -44093,7 +44085,7 @@
           <t>B | 1187呎 (3房)
 $4439万
 $37,400/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44108,7 +44100,7 @@
           <t>A | 1523呎 (3房)
 $5969万
 $39,190/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -44116,7 +44108,7 @@
           <t>B | 1187呎 (3房)
 $4380万
 $36,900/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -44131,7 +44123,7 @@
           <t>A | 1523呎 (3房)
 $5986万
 $39,307/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -44139,7 +44131,7 @@
           <t>B | 1187呎 (3房)
 $4356万
 $36,700/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -44154,7 +44146,7 @@
           <t>A | 1523呎 (3房)
 $5840万
 $38,346/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -44162,7 +44154,7 @@
           <t>B | 1187呎 (3房)
 $4321万
 $36,400/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -44177,7 +44169,7 @@
           <t>A | 1523呎 (3房)
 $5457万
 $35,830/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -44185,7 +44177,7 @@
           <t>B | 1187呎 (3房)
 $4285万
 $36,100/呎
-(23年-03月-22日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -44200,7 +44192,7 @@
           <t>A | 1523呎 (3房)
 $5393万
 $35,410/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -44208,7 +44200,7 @@
           <t>B | 1187呎 (3房)
 $4500万
 $37,911/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -44223,7 +44215,7 @@
           <t>A | 1523呎 (3房)
 $5313万
 $34,882/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -44231,7 +44223,7 @@
           <t>B | 1135呎 (3房)
 $4214万
 $37,126/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -44246,7 +44238,7 @@
           <t>A | 1523呎 (3房)
 $5474万
 $35,942/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -44254,7 +44246,7 @@
           <t>B | 1187呎 (3房)
 $4851万
 $40,867/呎
-(23年-03月-19日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -44269,7 +44261,7 @@
           <t>A | 1523呎 (3房)
 $5387万
 $35,369/呎
-(24年-10月-09日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -44277,7 +44269,7 @@
           <t>B | 1187呎 (3房)
 $4330万
 $36,477/呎
-(23年-02月-21日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -44292,7 +44284,7 @@
           <t>A | 1523呎 (3房)
 $4980万
 $32,700/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -44300,7 +44292,7 @@
           <t>B | 1187呎 (3房)
 $3960万
 $33,361/呎
-(23年-02月-21日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -44315,7 +44307,7 @@
           <t>A | 1523呎 (3房)
 $5364万
 $35,217/呎
-(24年-03月-12日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -44323,7 +44315,7 @@
           <t>B | 1187呎 (3房)
 $4095万
 $34,500/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -44338,7 +44330,7 @@
           <t>A | 1525呎 (3房)
 $4926万
 $32,300/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -44346,7 +44338,7 @@
           <t>B | 1185呎 (3房)
 $4206万
 $35,494/呎
-(23年-05月-16日)</t>
+(23年-05月)</t>
         </is>
       </c>
     </row>
@@ -44361,7 +44353,7 @@
           <t>A | 1525呎 (3房)
 $4956万
 $32,498/呎
-(23年-07月-10日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -44369,7 +44361,7 @@
           <t>B | 1185呎 (3房)
 $4468万
 $37,705/呎
-(22年-12月-07日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -44384,7 +44376,7 @@
           <t>A | 1525呎 (3房)
 $5002万
 $32,800/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -44392,7 +44384,7 @@
           <t>B | 1185呎 (3房)
 $4005万
 $33,800/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -44407,7 +44399,7 @@
           <t>A | 1525呎 (3房)
 $5265万
 $34,525/呎
-(23年-02月-14日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -44415,7 +44407,7 @@
           <t>B | 1185呎 (3房)
 $4092万
 $34,531/呎
-(23年-02月-14日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -44430,7 +44422,7 @@
           <t>A | 1525呎 (3房)
 $4773万
 $31,300/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -44438,7 +44430,7 @@
           <t>B | 1185呎 (3房)
 $3922万
 $33,100/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -44453,7 +44445,7 @@
           <t>A | 1525呎 (3房)
 $5261万
 $34,497/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -44461,7 +44453,7 @@
           <t>B | 1185呎 (3房)
 $4100万
 $34,599/呎
-(23年-02月-22日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -44476,7 +44468,7 @@
           <t>A | 1525呎 (3房)
 $5101万
 $33,450/呎
-(22年-12月-11日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -44484,7 +44476,7 @@
           <t>B | 1185呎 (3房)
 $4337万
 $36,596/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -44499,7 +44491,7 @@
           <t>A | 1525呎 (3房)
 $4712万
 $30,900/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -44507,7 +44499,7 @@
           <t>B | 1185呎 (3房)
 $4039万
 $34,084/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -44522,7 +44514,7 @@
           <t>A | 1525呎 (3房)
 $5119万
 $33,566/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -44530,7 +44522,7 @@
           <t>B | 1185呎 (3房)
 $4317万
 $36,433/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -44545,7 +44537,7 @@
           <t>A | 1525呎 (3房)
 $4888万
 $32,050/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -44553,7 +44545,7 @@
           <t>B | 1185呎 (3房)
 $3389万
 $28,600/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44568,7 +44560,7 @@
           <t>A | 1525呎 (3房)
 $4333万
 $28,410/呎
-(25年-04月-15日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -44576,7 +44568,7 @@
           <t>B | 1185呎 (3房)
 $3300万
 $27,848/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44591,7 +44583,7 @@
           <t>A | 1525呎 (3房)
 $4049万
 $26,552/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -44599,7 +44591,7 @@
           <t>B | 1185呎 (3房)
 $3261万
 $27,522/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -44614,7 +44606,7 @@
           <t>A | 1525呎 (3房)
 $4380万
 $28,720/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -44622,7 +44614,7 @@
           <t>B | 1185呎 (3房)
 $3072万
 $25,920/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -44637,7 +44629,7 @@
           <t>A | 1525呎 (3房)
 $4376万
 $28,692/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -44645,7 +44637,7 @@
           <t>B | 1185呎 (3房)
 $2978万
 $25,131/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -44660,7 +44652,7 @@
           <t>A | 1466呎 (3房)
 $4217万
 $28,768/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -44668,7 +44660,7 @@
           <t>B | 1146呎 (3房)
 $2904万
 $25,336/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -44800,7 +44792,7 @@
         <is>
           <t>Mansion A (Harbour Light)
 4636呎 (4+房)
-(24年-06月-27日)
+(24年-06月)
 $3.40亿
 $73,339/呎</t>
         </is>

--- a/files/九龙-启德-沄璟.xlsx
+++ b/files/九龙-启德-沄璟.xlsx
@@ -37949,7 +37949,7 @@
           <t>A | 2088呎 (4+房)
 $12605万
 $60,370/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -37972,7 +37972,7 @@
           <t>A | 2034呎 (4+房)
 $12522万
 $61,562/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -37995,7 +37995,7 @@
           <t>A | 2088呎 (4+房)
 $12446万
 $59,609/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -38041,7 +38041,7 @@
           <t>A | 2088呎 (4+房)
 $11761万
 $56,327/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38049,7 +38049,7 @@
           <t>B | 1870呎 (4+房)
 $9483万
 $50,710/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -38064,7 +38064,7 @@
           <t>A | 2088呎 (4+房)
 $12055万
 $57,737/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38072,7 +38072,7 @@
           <t>B | 1870呎 (4+房)
 $8796万
 $47,036/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -38087,7 +38087,7 @@
           <t>A | 2088呎 (4+房)
 $11467万
 $54,916/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38095,7 +38095,7 @@
           <t>B | 1870呎 (4+房)
 $9233万
 $49,376/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -38110,7 +38110,7 @@
           <t>A | 2088呎 (4+房)
 $10557万
 $50,561/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -38133,7 +38133,7 @@
           <t>A | 2088呎 (4+房)
 $12038万
 $57,653/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38141,7 +38141,7 @@
           <t>B | 1870呎 (4+房)
 $9278万
 $49,617/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -38156,7 +38156,7 @@
           <t>A | 2088呎 (4+房)
 $10255万
 $49,113/呎
-(23年-02月)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38164,7 +38164,7 @@
           <t>B | 1870呎 (4+房)
 $8013万
 $42,850/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -38179,7 +38179,7 @@
           <t>A | 2088呎 (4+房)
 $10110万
 $48,419/呎
-(23年-01月)</t>
+(23年-01月-30日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38187,7 +38187,7 @@
           <t>B | 1816呎 (4+房)
 $9054万
 $49,856/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -38202,7 +38202,7 @@
           <t>A | 2088呎 (4+房)
 $10252万
 $49,100/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38210,7 +38210,7 @@
           <t>B | 1870呎 (4+房)
 $8578万
 $45,870/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -38225,7 +38225,7 @@
           <t>A | 2088呎 (4+房)
 $10085万
 $48,300/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -38233,7 +38233,7 @@
           <t>B | 1870呎 (4+房)
 $8929万
 $47,748/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -38248,7 +38248,7 @@
           <t>A | 2088呎 (4+房)
 $10117万
 $48,453/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -38256,7 +38256,7 @@
           <t>B | 1816呎 (4+房)
 $8690万
 $47,852/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38271,7 @@
           <t>A | 2088呎 (4+房)
 $9855万
 $47,200/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -38279,7 +38279,7 @@
           <t>B | 1870呎 (4+房)
 $8308万
 $44,429/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -38294,7 +38294,7 @@
           <t>A | 2088呎 (4+房)
 $9587万
 $45,913/呎
-(23年-02月)</t>
+(23年-02月-14日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -38302,7 +38302,7 @@
           <t>B | 1870呎 (4+房)
 $8207万
 $43,889/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -38317,7 +38317,7 @@
           <t>A | 2088呎 (4+房)
 $9324万
 $44,653/呎
-(23年-01月)</t>
+(23年-01月-30日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -38325,7 +38325,7 @@
           <t>B | 1870呎 (4+房)
 $8477万
 $45,333/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -38340,7 +38340,7 @@
           <t>A | 2088呎 (4+房)
 $9542万
 $45,700/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -38348,7 +38348,7 @@
           <t>B | 1870呎 (4+房)
 $7386万
 $39,500/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -38363,7 +38363,7 @@
           <t>A | 2088呎 (4+房)
 $9420万
 $45,115/呎
-(23年-01月)</t>
+(23年-01月-19日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -38371,7 +38371,7 @@
           <t>B | 1870呎 (4+房)
 $7939万
 $42,457/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -38386,7 +38386,7 @@
           <t>A | 2088呎 (4+房)
 $8403万
 $40,242/呎
-(23年-01月)</t>
+(23年-01月-12日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -38394,7 +38394,7 @@
           <t>B | 1870呎 (4+房)
 $7315万
 $39,120/呎
-(23年-01月)</t>
+(23年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -38409,7 +38409,7 @@
           <t>A | 2088呎 (4+房)
 $8456万
 $40,500/呎
-(23年-03月)</t>
+(23年-03月-01日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -38417,7 +38417,7 @@
           <t>B | 1870呎 (4+房)
 $7143万
 $38,200/呎
-(23年-03月)</t>
+(23年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -38432,7 +38432,7 @@
           <t>A | 2088呎 (4+房)
 $9271万
 $44,400/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>B | 1870呎 (4+房)
 $8182万
 $43,753/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -38455,7 +38455,7 @@
           <t>A | 2088呎 (4+房)
 $9703万
 $46,472/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -38463,7 +38463,7 @@
           <t>B | 1870呎 (4+房)
 $7750万
 $41,444/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -38478,7 +38478,7 @@
           <t>A | 2088呎 (4+房)
 $9127万
 $43,710/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -38486,7 +38486,7 @@
           <t>B | 1870呎 (4+房)
 $7696万
 $41,157/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
     </row>
@@ -38501,7 +38501,7 @@
           <t>A | 2088呎 (4+房)
 $9427万
 $45,150/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -38509,7 +38509,7 @@
           <t>B | 1870呎 (4+房)
 $7684万
 $41,089/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -38524,7 +38524,7 @@
           <t>A | 1985呎 (4+房)
 $8658万
 $43,617/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -38532,7 +38532,7 @@
           <t>B | 1797呎 (4+房)
 $7178万
 $39,946/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -38773,7 +38773,7 @@
           <t>A | 1909呎 (4+房)
 $9704万
 $50,832/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38781,7 +38781,7 @@
           <t>B | 1870呎 (4+房)
 $9146万
 $48,910/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -38850,7 +38850,7 @@
           <t>B | 1870呎 (4+房)
 $8415万
 $45,000/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -38865,7 +38865,7 @@
           <t>A | 1909呎 (4+房)
 $9434万
 $49,421/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -38888,7 +38888,7 @@
           <t>A | 1909呎 (4+房)
 $9490万
 $49,712/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -38911,7 +38911,7 @@
           <t>A | 1909呎 (4+房)
 $8880万
 $46,517/呎
-(23年-02月)</t>
+(23年-02月-12日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -38934,7 +38934,7 @@
           <t>A | 1909呎 (4+房)
 $9295万
 $48,690/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -38957,7 +38957,7 @@
           <t>A | 1909呎 (4+房)
 $9015万
 $47,221/呎
-(23年-07月)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38965,7 +38965,7 @@
           <t>B | 1816呎 (4+房)
 $9086万
 $50,033/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -38980,7 +38980,7 @@
           <t>A | 1909呎 (4+房)
 $9017万
 $47,236/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -39003,7 +39003,7 @@
           <t>A | 1909呎 (4+房)
 $8552万
 $44,800/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -39011,7 +39011,7 @@
           <t>B | 1870呎 (4+房)
 $8265万
 $44,200/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -39026,7 +39026,7 @@
           <t>A | 1909呎 (4+房)
 $8837万
 $46,290/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -39049,7 +39049,7 @@
           <t>A | 1909呎 (4+房)
 $8302万
 $43,490/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -39057,7 +39057,7 @@
           <t>B | 1870呎 (4+房)
 $8103万
 $43,329/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -39072,7 +39072,7 @@
           <t>A | 1909呎 (4+房)
 $7865万
 $41,200/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -39080,7 +39080,7 @@
           <t>B | 1870呎 (4+房)
 $7667万
 $41,000/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -39095,7 +39095,7 @@
           <t>A | 1909呎 (4+房)
 $7770万
 $40,700/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -39103,7 +39103,7 @@
           <t>B | 1870呎 (4+房)
 $7574万
 $40,500/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -39118,7 +39118,7 @@
           <t>A | 1909呎 (4+房)
 $8062万
 $42,231/呎
-(24年-07月)</t>
+(24年-07月-21日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -39126,7 +39126,7 @@
           <t>B | 1870呎 (4+房)
 $8054万
 $43,070/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -39141,7 +39141,7 @@
           <t>A | 1909呎 (4+房)
 $8319万
 $43,579/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -39149,7 +39149,7 @@
           <t>B | 1870呎 (4+房)
 $7630万
 $40,800/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -39164,7 +39164,7 @@
           <t>A | 1909呎 (4+房)
 $7882万
 $41,290/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39172,7 +39172,7 @@
           <t>B | 1870呎 (4+房)
 $7904万
 $42,270/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -39187,7 +39187,7 @@
           <t>A | 1909呎 (4+房)
 $7470万
 $39,130/呎
-(23年-07月)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39195,7 +39195,7 @@
           <t>B | 1870呎 (4+房)
 $7860万
 $42,029/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -39210,7 +39210,7 @@
           <t>A | 1909呎 (4+房)
 $8131万
 $42,595/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -39218,7 +39218,7 @@
           <t>B | 1870呎 (4+房)
 $7800万
 $41,710/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -39233,7 +39233,7 @@
           <t>A | 1909呎 (4+房)
 $8104万
 $42,453/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -39241,7 +39241,7 @@
           <t>B | 1870呎 (4+房)
 $8167万
 $43,673/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -39256,7 +39256,7 @@
           <t>A | 1909呎 (4+房)
 $7708万
 $40,377/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -39264,7 +39264,7 @@
           <t>B | 1870呎 (4+房)
 $7532万
 $40,276/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -39279,7 +39279,7 @@
           <t>A | 1909呎 (4+房)
 $7292万
 $38,200/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -39287,7 +39287,7 @@
           <t>B | 1870呎 (4+房)
 $7704万
 $41,196/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -39302,7 +39302,7 @@
           <t>A | 1909呎 (4+房)
 $7576万
 $39,687/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -39310,7 +39310,7 @@
           <t>B | 1816呎 (4+房)
 $7996万
 $44,028/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -39325,7 +39325,7 @@
           <t>A | 1828呎 (4+房)
 $7534万
 $41,213/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -39333,7 +39333,7 @@
           <t>B | 1797呎 (4+房)
 $7380万
 $41,069/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -39471,7 +39471,7 @@
           <t>A | 1129呎 (3房)
 $5215万
 $46,195/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -39479,7 +39479,7 @@
           <t>B | 1334呎 (3房)
 $3869万
 $29,000/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr"/>
@@ -39496,7 +39496,7 @@
           <t>A | 577呎 (2房)
 $1546万
 $26,800/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -39504,7 +39504,7 @@
           <t>B | 554呎 (2房)
 $1391万
 $25,100/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -39535,7 +39535,7 @@
           <t>A | 577呎 (2房)
 $1512万
 $26,200/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -39543,7 +39543,7 @@
           <t>B | 553呎 (2房)
 $1363万
 $24,644/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>A | 577呎 (2房)
 $1489万
 $25,810/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>B | 554呎 (2房)
 $1324万
 $23,900/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39652,7 +39652,7 @@
           <t>A | 577呎 (2房)
 $1482万
 $25,681/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -39660,7 +39660,7 @@
           <t>B | 553呎 (2房)
 $1319万
 $23,843/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39691,7 +39691,7 @@
           <t>A | 577呎 (2房)
 $1474万
 $25,554/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -39699,7 +39699,7 @@
           <t>B | 553呎 (2房)
 $1341万
 $24,244/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -39730,7 +39730,7 @@
           <t>A | 577呎 (2房)
 $1467万
 $25,426/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -39738,7 +39738,7 @@
           <t>B | 554呎 (2房)
 $1335万
 $24,100/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -39769,7 +39769,7 @@
           <t>A | 577呎 (2房)
 $1460万
 $25,300/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39777,7 +39777,7 @@
           <t>B | 554呎 (2房)
 $1319万
 $23,800/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39808,7 +39808,7 @@
           <t>A | 577呎 (2房)
 $1469万
 $25,454/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39816,7 +39816,7 @@
           <t>B | 554呎 (2房)
 $1285万
 $23,200/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>C | 509呎 (2房)
 $1196万
 $23,500/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -39847,7 +39847,7 @@
           <t>A | 577呎 (2房)
 $1438万
 $24,925/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39855,7 +39855,7 @@
           <t>B | 554呎 (2房)
 $1274万
 $23,000/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -39863,7 +39863,7 @@
           <t>C | 509呎 (2房)
 $1191万
 $23,400/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -39886,7 +39886,7 @@
           <t>A | 577呎 (2房)
 $1431万
 $24,801/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39894,7 +39894,7 @@
           <t>B | 554呎 (2房)
 $1269万
 $22,900/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -39902,7 +39902,7 @@
           <t>C | 509呎 (2房)
 $1186万
 $23,300/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -39925,7 +39925,7 @@
           <t>A | 577呎 (2房)
 $1424万
 $24,677/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -39933,7 +39933,7 @@
           <t>B | 553呎 (2房)
 $1302万
 $23,542/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39964,7 +39964,7 @@
           <t>A | 577呎 (2房)
 $1417万
 $24,555/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -39972,7 +39972,7 @@
           <t>B | 554呎 (2房)
 $1280万
 $23,100/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -40003,7 +40003,7 @@
           <t>A | 577呎 (2房)
 $1410万
 $24,432/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -40011,7 +40011,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40042,7 +40042,7 @@
           <t>A | 577呎 (2房)
 $1403万
 $24,311/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40050,7 +40050,7 @@
           <t>B | 553呎 (2房)
 $1285万
 $23,242/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40081,7 +40081,7 @@
           <t>A | 577呎 (2房)
 $1411万
 $24,459/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -40089,7 +40089,7 @@
           <t>B | 554呎 (2房)
 $1280万
 $23,100/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -40120,7 +40120,7 @@
           <t>A | 577呎 (2房)
 $1389万
 $24,070/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40128,7 +40128,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40159,7 +40159,7 @@
           <t>A | 577呎 (2房)
 $1382万
 $23,950/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40167,7 +40167,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40198,7 +40198,7 @@
           <t>A | 577呎 (2房)
 $1368万
 $23,713/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40206,7 +40206,7 @@
           <t>B | 554呎 (2房)
 $1258万
 $22,700/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -40214,7 +40214,7 @@
           <t>C | 509呎 (2房)
 $1155万
 $22,700/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -40237,7 +40237,7 @@
           <t>A | 577呎 (2房)
 $1361万
 $23,595/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40245,7 +40245,7 @@
           <t>B | 553呎 (2房)
 $1252万
 $22,641/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -40253,7 +40253,7 @@
           <t>C | 509呎 (2房)
 $1150万
 $22,600/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -40276,7 +40276,7 @@
           <t>A | 577呎 (2房)
 $1355万
 $23,477/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40284,7 +40284,7 @@
           <t>B | 554呎 (2房)
 $1295万
 $23,377/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -40315,7 +40315,7 @@
           <t>A | 577呎 (2房)
 $1348万
 $23,361/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40323,7 +40323,7 @@
           <t>B | 553呎 (2房)
 $1252万
 $22,641/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40354,7 +40354,7 @@
           <t>A | 577呎 (2房)
 $1341万
 $23,244/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40362,7 +40362,7 @@
           <t>B | 554呎 (2房)
 $1246万
 $22,500/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40393,7 +40393,7 @@
           <t>A | 577呎 (2房)
 $1335万
 $23,129/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -40401,7 +40401,7 @@
           <t>B | 554呎 (2房)
 $1235万
 $22,300/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40432,7 +40432,7 @@
           <t>A | 577呎 (2房)
 $1247万
 $21,606/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40471,7 +40471,7 @@
           <t>A | 577呎 (2房)
 $1210万
 $20,976/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40510,7 +40510,7 @@
           <t>A | 577呎 (2房)
 $1198万
 $20,769/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40549,7 +40549,7 @@
           <t>A | 577呎 (2房)
 $1195万
 $20,706/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -40588,7 +40588,7 @@
           <t>A | 577呎 (2房)
 $1191万
 $20,644/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -40627,7 +40627,7 @@
           <t>A | 539呎 (2房)
 $1197万
 $22,200/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -40800,7 +40800,7 @@
           <t>A | 659呎 (2房)
 $1799万
 $27,300/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -40808,7 +40808,7 @@
           <t>B | 523呎 (2房)
 $1423万
 $27,200/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -40816,7 +40816,7 @@
           <t>C | 568呎 (2房)
 $1551万
 $27,300/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -40831,7 +40831,7 @@
           <t>A | 659呎 (2房)
 $1766万
 $26,800/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -40839,7 +40839,7 @@
           <t>B | 523呎 (2房)
 $1396万
 $26,700/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -40847,7 +40847,7 @@
           <t>C | 568呎 (2房)
 $1522万
 $26,800/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -40862,7 +40862,7 @@
           <t>A | 659呎 (2房)
 $1746万
 $26,500/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -40870,7 +40870,7 @@
           <t>B | 523呎 (2房)
 $1381万
 $26,400/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -40878,7 +40878,7 @@
           <t>C | 568呎 (2房)
 $1505万
 $26,500/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -40893,7 +40893,7 @@
           <t>A | 659呎 (2房)
 $1735万
 $26,323/呎
-(25年-03月)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -40901,7 +40901,7 @@
           <t>B | 523呎 (2房)
 $1371万
 $26,205/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -40909,7 +40909,7 @@
           <t>C | 1644呎 (2房)
 $1496万
 $9,099/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -40924,7 +40924,7 @@
           <t>A | 659呎 (2房)
 $1726万
 $26,192/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -40932,7 +40932,7 @@
           <t>B | 523呎 (2房)
 $1364万
 $26,075/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -40940,7 +40940,7 @@
           <t>C | 568呎 (2房)
 $1488万
 $26,205/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -40955,7 +40955,7 @@
           <t>A | 659呎 (2房)
 $1717万
 $26,062/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -40963,7 +40963,7 @@
           <t>B | 523呎 (2房)
 $1357万
 $25,945/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -40971,7 +40971,7 @@
           <t>C | 568呎 (2房)
 $1481万
 $26,075/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -40986,7 +40986,7 @@
           <t>A | 659呎 (2房)
 $1709万
 $25,932/呎
-(25年-06月)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -40994,7 +40994,7 @@
           <t>B | 523呎 (2房)
 $1350万
 $25,816/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41002,7 +41002,7 @@
           <t>C | 568呎 (2房)
 $1474万
 $25,945/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -41017,7 +41017,7 @@
           <t>A | 659呎 (2房)
 $1700万
 $25,803/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -41025,7 +41025,7 @@
           <t>B | 523呎 (2房)
 $1343万
 $25,688/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41033,7 +41033,7 @@
           <t>C | 568呎 (2房)
 $1466万
 $25,816/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -41048,7 +41048,7 @@
           <t>A | 659呎 (2房)
 $1692万
 $25,675/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -41056,7 +41056,7 @@
           <t>B | 523呎 (2房)
 $1337万
 $25,560/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41064,7 +41064,7 @@
           <t>C | 568呎 (2房)
 $1459万
 $25,688/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41079,7 +41079,7 @@
           <t>A | 659呎 (2房)
 $1675万
 $25,421/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -41087,7 +41087,7 @@
           <t>B | 523呎 (2房)
 $1324万
 $25,307/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41095,7 +41095,7 @@
           <t>C | 568呎 (2房)
 $1445万
 $25,433/呎
-(24年-06月)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -41110,7 +41110,7 @@
           <t>A | 659呎 (2房)
 $1667万
 $25,294/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -41118,7 +41118,7 @@
           <t>B | 523呎 (2房)
 $1317万
 $25,181/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41126,7 +41126,7 @@
           <t>C | 568呎 (2房)
 $1437万
 $25,307/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
           <t>A | 659呎 (2房)
 $1659万
 $25,168/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -41149,7 +41149,7 @@
           <t>B | 523呎 (2房)
 $1310万
 $25,056/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41157,7 +41157,7 @@
           <t>C | 568呎 (2房)
 $1430万
 $25,181/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -41172,7 +41172,7 @@
           <t>A | 659呎 (2房)
 $1650万
 $25,043/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -41180,7 +41180,7 @@
           <t>B | 523呎 (2房)
 $1304万
 $24,931/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41188,7 +41188,7 @@
           <t>C | 568呎 (2房)
 $1423万
 $25,056/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -41203,7 +41203,7 @@
           <t>A | 659呎 (2房)
 $1642万
 $24,919/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -41211,7 +41211,7 @@
           <t>B | 523呎 (2房)
 $1297万
 $24,807/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41219,7 +41219,7 @@
           <t>C | 568呎 (2房)
 $1416万
 $24,931/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -41234,7 +41234,7 @@
           <t>A | 659呎 (2房)
 $1634万
 $24,795/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -41242,7 +41242,7 @@
           <t>B | 523呎 (2房)
 $1291万
 $24,684/呎
-(24年-07月)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>C | 568呎 (2房)
 $1409万
 $24,807/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -41265,7 +41265,7 @@
           <t>A | 656呎 (2房)
 $1618万
 $24,671/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -41273,7 +41273,7 @@
           <t>B | 526呎 (2房)
 $1292万
 $24,561/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41281,7 +41281,7 @@
           <t>C | 568呎 (2房)
 $1402万
 $24,684/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -41296,7 +41296,7 @@
           <t>A | 656呎 (2房)
 $1610万
 $24,549/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -41304,7 +41304,7 @@
           <t>B | 526呎 (2房)
 $1285万
 $24,439/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41312,7 +41312,7 @@
           <t>C | 568呎 (2房)
 $1395万
 $24,561/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -41327,7 +41327,7 @@
           <t>A | 656呎 (2房)
 $1602万
 $24,427/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -41335,7 +41335,7 @@
           <t>B | 526呎 (2房)
 $1279万
 $24,317/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41343,7 +41343,7 @@
           <t>C | 568呎 (2房)
 $1388万
 $24,439/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -41358,7 +41358,7 @@
           <t>A | 656呎 (2房)
 $1587万
 $24,185/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -41366,7 +41366,7 @@
           <t>B | 526呎 (2房)
 $1266万
 $24,076/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41374,7 +41374,7 @@
           <t>C | 568呎 (2房)
 $1374万
 $24,197/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -41389,7 +41389,7 @@
           <t>A | 656呎 (2房)
 $1579万
 $24,064/呎
-(24年-07月)</t>
+(24年-07月-28日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -41397,7 +41397,7 @@
           <t>B | 526呎 (2房)
 $1260万
 $23,956/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41405,7 +41405,7 @@
           <t>C | 568呎 (2房)
 $1368万
 $24,076/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -41420,7 +41420,7 @@
           <t>A | 656呎 (2房)
 $1571万
 $23,945/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -41428,7 +41428,7 @@
           <t>B | 526呎 (2房)
 $1254万
 $23,837/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41436,7 +41436,7 @@
           <t>C | 568呎 (2房)
 $1376万
 $24,223/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -41451,7 +41451,7 @@
           <t>A | 656呎 (2房)
 $1563万
 $23,825/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -41459,7 +41459,7 @@
           <t>B | 526呎 (2房)
 $1248万
 $23,719/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41467,7 +41467,7 @@
           <t>C | 568呎 (2房)
 $1354万
 $23,837/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -41482,7 +41482,7 @@
           <t>A | 656呎 (2房)
 $1555万
 $23,707/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -41490,7 +41490,7 @@
           <t>B | 526呎 (2房)
 $1241万
 $23,601/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41498,7 +41498,7 @@
           <t>C | 568呎 (2房)
 $1347万
 $23,719/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -41513,7 +41513,7 @@
           <t>A | 656呎 (2房)
 $1547万
 $23,589/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -41521,7 +41521,7 @@
           <t>B | 526呎 (2房)
 $1235万
 $23,483/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -41529,7 +41529,7 @@
           <t>C | 568呎 (2房)
 $1355万
 $23,863/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -41544,7 +41544,7 @@
           <t>A | 656呎 (2房)
 $1429万
 $21,790/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -41552,7 +41552,7 @@
           <t>B | 526呎 (2房)
 $1158万
 $22,014/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -41560,7 +41560,7 @@
           <t>C | 568呎 (2房)
 $1250万
 $22,014/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
     </row>
@@ -41575,7 +41575,7 @@
           <t>A | 656呎 (2房)
 $1361万
 $20,752/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -41583,7 +41583,7 @@
           <t>B | 526呎 (2房)
 $1103万
 $20,966/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -41591,7 +41591,7 @@
           <t>C | 568呎 (2房)
 $1191万
 $20,966/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -41606,7 +41606,7 @@
           <t>A | 656呎 (2房)
 $1335万
 $20,345/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -41614,7 +41614,7 @@
           <t>B | 526呎 (2房)
 $1081万
 $20,555/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -41622,7 +41622,7 @@
           <t>C | 568呎 (2房)
 $1179万
 $20,758/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -41637,7 +41637,7 @@
           <t>A | 656呎 (2房)
 $1331万
 $20,284/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -41645,7 +41645,7 @@
           <t>B | 526呎 (2房)
 $1078万
 $20,493/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -41653,7 +41653,7 @@
           <t>C | 568呎 (2房)
 $1176万
 $20,696/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -41668,7 +41668,7 @@
           <t>A | 656呎 (2房)
 $1327万
 $20,223/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -41676,7 +41676,7 @@
           <t>B | 526呎 (2房)
 $1075万
 $20,432/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -41684,7 +41684,7 @@
           <t>C | 568呎 (2房)
 $1172万
 $20,634/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -41699,7 +41699,7 @@
           <t>A | 618呎 (2房)
 $1259万
 $20,371/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -41707,7 +41707,7 @@
           <t>B | 488呎 (2房)
 $1014万
 $20,787/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -41715,7 +41715,7 @@
           <t>C | 530呎 (2房)
 $1166万
 $22,000/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -41864,7 +41864,7 @@
           <t>A | 903呎 (3房)
 $3070万
 $33,998/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -41872,7 +41872,7 @@
           <t>B | 564呎 (2房)
 $1884万
 $33,400/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -41880,7 +41880,7 @@
           <t>C | 620呎 (2房)
 $1978万
 $31,900/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -41895,7 +41895,7 @@
           <t>A | 903呎 (3房)
 $3043万
 $33,700/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -41903,7 +41903,7 @@
           <t>B | 564呎 (2房)
 $1844万
 $32,700/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -41911,7 +41911,7 @@
           <t>C | 620呎 (2房)
 $1941万
 $31,300/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -41926,7 +41926,7 @@
           <t>A | 900呎 (3房)
 $3043万
 $33,812/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -41934,7 +41934,7 @@
           <t>B | 564呎 (2房)
 $1827万
 $32,400/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -41942,7 +41942,7 @@
           <t>C | 620呎 (2房)
 $1916万
 $30,900/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -41957,7 +41957,7 @@
           <t>A | 903呎 (3房)
 $2935万
 $32,500/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -41965,7 +41965,7 @@
           <t>B | 564呎 (2房)
 $1816万
 $32,200/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -41973,7 +41973,7 @@
           <t>C | 620呎 (2房)
 $1904万
 $30,712/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -41988,7 +41988,7 @@
           <t>A | 903呎 (3房)
 $2946万
 $32,623/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -41996,7 +41996,7 @@
           <t>B | 564呎 (2房)
 $1805万
 $32,000/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -42004,7 +42004,7 @@
           <t>C | 620呎 (2房)
 $1914万
 $30,868/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -42019,7 +42019,7 @@
           <t>A | 903呎 (3房)
 $2899万
 $32,100/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -42027,7 +42027,7 @@
           <t>B | 564呎 (2房)
 $1794万
 $31,800/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -42035,7 +42035,7 @@
           <t>C | 620呎 (2房)
 $1902万
 $30,684/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -42050,7 +42050,7 @@
           <t>A | 903呎 (3房)
 $2935万
 $32,500/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -42058,7 +42058,7 @@
           <t>B | 564呎 (2房)
 $1782万
 $31,600/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -42066,7 +42066,7 @@
           <t>C | 620呎 (2房)
 $1870万
 $30,165/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -42081,7 +42081,7 @@
           <t>A | 903呎 (3房)
 $2862万
 $31,700/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -42089,7 +42089,7 @@
           <t>B | 564呎 (2房)
 $1771万
 $31,400/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -42097,7 +42097,7 @@
           <t>C | 620呎 (2房)
 $1859万
 $29,985/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -42112,7 +42112,7 @@
           <t>A | 903呎 (3房)
 $2872万
 $31,805/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -42120,7 +42120,7 @@
           <t>B | 564呎 (2房)
 $1760万
 $31,200/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -42128,7 +42128,7 @@
           <t>C | 620呎 (2房)
 $1848万
 $29,807/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -42143,7 +42143,7 @@
           <t>A | 903呎 (3房)
 $2946万
 $32,630/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -42151,7 +42151,7 @@
           <t>B | 564呎 (2房)
 $1779万
 $31,534/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -42159,7 +42159,7 @@
           <t>C | 620呎 (2房)
 $1828万
 $29,482/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -42174,7 +42174,7 @@
           <t>A | 903呎 (3房)
 $3180万
 $35,217/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -42182,7 +42182,7 @@
           <t>B | 564呎 (2房)
 $1687万
 $29,917/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -42190,7 +42190,7 @@
           <t>C | 620呎 (2房)
 $1781万
 $28,732/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42205,7 +42205,7 @@
           <t>A | 903呎 (3房)
 $2781万
 $30,800/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -42213,7 +42213,7 @@
           <t>B | 564呎 (2房)
 $1719万
 $30,482/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -42221,7 +42221,7 @@
           <t>C | 620呎 (2房)
 $1790万
 $28,878/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -42236,7 +42236,7 @@
           <t>A | 903呎 (3房)
 $2798万
 $30,982/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -42244,7 +42244,7 @@
           <t>B | 564呎 (2房)
 $1709万
 $30,300/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -42252,7 +42252,7 @@
           <t>C | 620呎 (2房)
 $1780万
 $28,706/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -42267,7 +42267,7 @@
           <t>A | 903呎 (3房)
 $2745万
 $30,400/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -42275,7 +42275,7 @@
           <t>B | 564呎 (2房)
 $1699万
 $30,119/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -42283,7 +42283,7 @@
           <t>C | 620呎 (2房)
 $1769万
 $28,534/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42298,7 +42298,7 @@
           <t>A | 903呎 (3房)
 $2764万
 $30,604/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -42306,7 +42306,7 @@
           <t>B | 564呎 (2房)
 $1689万
 $29,939/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -42314,7 +42314,7 @@
           <t>C | 620呎 (2房)
 $1759万
 $28,364/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
           <t>A | 902呎 (3房)
 $2867万
 $31,785/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -42337,7 +42337,7 @@
           <t>B | 567呎 (2房)
 $1725万
 $30,422/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -42345,7 +42345,7 @@
           <t>C | 619呎 (2房)
 $1726万
 $27,885/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -42360,7 +42360,7 @@
           <t>A | 902呎 (3房)
 $2697万
 $29,900/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -42368,7 +42368,7 @@
           <t>B | 567呎 (2房)
 $1677万
 $29,583/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -42376,7 +42376,7 @@
           <t>C | 619呎 (2房)
 $1716万
 $27,719/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42391,7 +42391,7 @@
           <t>A | 902呎 (3房)
 $2679万
 $29,700/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -42399,7 +42399,7 @@
           <t>B | 567呎 (2房)
 $1667万
 $29,407/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -42407,7 +42407,7 @@
           <t>C | 619呎 (2房)
 $1725万
 $27,860/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42422,7 +42422,7 @@
           <t>A | 902呎 (3房)
 $2661万
 $29,500/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -42430,7 +42430,7 @@
           <t>B | 567呎 (2房)
 $1627万
 $28,693/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -42438,7 +42438,7 @@
           <t>C | 619呎 (2房)
 $1706万
 $27,557/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -42453,7 +42453,7 @@
           <t>A | 902呎 (3房)
 $2634万
 $29,200/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -42461,7 +42461,7 @@
           <t>B | 567呎 (2房)
 $1617万
 $28,522/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -42469,7 +42469,7 @@
           <t>C | 619呎 (2房)
 $1677万
 $27,091/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -42484,7 +42484,7 @@
           <t>A | 902呎 (3房)
 $2713万
 $30,082/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -42492,7 +42492,7 @@
           <t>B | 567呎 (2房)
 $1590万
 $28,040/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -42500,7 +42500,7 @@
           <t>C | 619呎 (2房)
 $1700万
 $27,468/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -42515,7 +42515,7 @@
           <t>A | 902呎 (3房)
 $2970万
 $32,924/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -42523,7 +42523,7 @@
           <t>B | 567呎 (2房)
 $1598万
 $28,183/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -42531,7 +42531,7 @@
           <t>C | 619呎 (2房)
 $1657万
 $26,769/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -42546,7 +42546,7 @@
           <t>A | 902呎 (3房)
 $2589万
 $28,700/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -42554,7 +42554,7 @@
           <t>B | 567呎 (2房)
 $1588万
 $28,014/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -42562,7 +42562,7 @@
           <t>C | 619呎 (2房)
 $1647万
 $26,609/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42577,7 +42577,7 @@
           <t>A | 902呎 (3房)
 $2571万
 $28,500/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -42585,7 +42585,7 @@
           <t>B | 567呎 (2房)
 $1562万
 $27,541/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -42593,7 +42593,7 @@
           <t>C | 619呎 (2房)
 $1637万
 $26,451/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -42608,7 +42608,7 @@
           <t>A | 902呎 (3房)
 $2526万
 $28,000/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -42616,7 +42616,7 @@
           <t>B | 567呎 (2房)
 $1442万
 $25,438/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -42624,7 +42624,7 @@
           <t>C | 619呎 (2房)
 $1530万
 $24,714/呎
-(25年-03月)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -42639,7 +42639,7 @@
           <t>A | 902呎 (3房)
 $2089万
 $23,156/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -42647,7 +42647,7 @@
           <t>B | 567呎 (2房)
 $1299万
 $22,917/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -42655,7 +42655,7 @@
           <t>C | 619呎 (2房)
 $1391万
 $22,468/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -42670,7 +42670,7 @@
           <t>A | 902呎 (3房)
 $1989万
 $22,053/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -42678,7 +42678,7 @@
           <t>B | 567呎 (2房)
 $1238万
 $21,826/呎
-(25年-03月)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -42686,7 +42686,7 @@
           <t>C | 619呎 (2房)
 $1337万
 $21,604/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -42701,7 +42701,7 @@
           <t>A | 902呎 (3房)
 $1983万
 $21,987/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -42709,7 +42709,7 @@
           <t>B | 567呎 (2房)
 $1234万
 $21,760/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -42717,7 +42717,7 @@
           <t>C | 619呎 (2房)
 $1333万
 $21,539/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -42732,7 +42732,7 @@
           <t>A | 902呎 (3房)
 $1977万
 $21,921/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -42740,7 +42740,7 @@
           <t>B | 567呎 (2房)
 $1230万
 $21,695/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -42748,7 +42748,7 @@
           <t>C | 619呎 (2房)
 $1329万
 $21,474/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -42763,7 +42763,7 @@
           <t>A | 869呎 (3房)
 $1921万
 $22,106/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -42771,7 +42771,7 @@
           <t>B | 529呎 (2房)
 $1165万
 $22,027/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -42779,7 +42779,7 @@
           <t>C | 597呎 (2房)
 $1292万
 $21,644/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -42928,7 +42928,7 @@
           <t>A | 950呎 (3房)
 $3515万
 $37,000/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -42936,7 +42936,7 @@
           <t>B | 781呎 (3房)
 $2761万
 $35,350/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -42944,7 +42944,7 @@
           <t>C | 903呎 (3房)
 $3133万
 $34,700/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -42959,7 +42959,7 @@
           <t>A | 950呎 (3房)
 $3397万
 $35,754/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -42967,7 +42967,7 @@
           <t>B | 781呎 (3房)
 $2706万
 $34,643/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -42975,7 +42975,7 @@
           <t>C | 903呎 (3房)
 $3101万
 $34,340/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
           <t>A | 950呎 (3房)
 $3473万
 $36,554/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -42998,7 +42998,7 @@
           <t>B | 781呎 (3房)
 $2773万
 $35,510/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -43006,7 +43006,7 @@
           <t>C | 903呎 (3房)
 $3043万
 $33,700/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -43021,7 +43021,7 @@
           <t>A | 950呎 (3房)
 $3914万
 $41,198/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -43029,7 +43029,7 @@
           <t>B | 781呎 (3房)
 $2666万
 $34,138/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -43037,7 +43037,7 @@
           <t>C | 903呎 (3房)
 $3025万
 $33,500/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -43052,7 +43052,7 @@
           <t>A | 950呎 (3房)
 $3539万
 $37,254/呎
-(23年-03月)</t>
+(23年-03月-05日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -43060,7 +43060,7 @@
           <t>B | 781呎 (3房)
 $2646万
 $33,880/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -43068,7 +43068,7 @@
           <t>C | 903呎 (3房)
 $3010万
 $33,330/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -43083,7 +43083,7 @@
           <t>A | 950呎 (3房)
 $3711万
 $39,061/呎
-(23年-03月)</t>
+(23年-03月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -43091,7 +43091,7 @@
           <t>B | 781呎 (3房)
 $2609万
 $33,400/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -43099,7 +43099,7 @@
           <t>C | 903呎 (3房)
 $2989万
 $33,100/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -43114,7 +43114,7 @@
           <t>A | 950呎 (3房)
 $3671万
 $38,638/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -43122,7 +43122,7 @@
           <t>B | 781呎 (3房)
 $2708万
 $34,674/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -43130,7 +43130,7 @@
           <t>C | 903呎 (3房)
 $3340万
 $36,992/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -43145,7 +43145,7 @@
           <t>A | 950呎 (3房)
 $3223万
 $33,928/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -43153,7 +43153,7 @@
           <t>B | 781呎 (3房)
 $2708万
 $34,677/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -43161,7 +43161,7 @@
           <t>C | 903呎 (3房)
 $2953万
 $32,700/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -43176,7 +43176,7 @@
           <t>A | 950呎 (3房)
 $3211万
 $33,800/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -43184,7 +43184,7 @@
           <t>B | 781呎 (3房)
 $2562万
 $32,800/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -43192,7 +43192,7 @@
           <t>C | 903呎 (3房)
 $3046万
 $33,734/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -43207,7 +43207,7 @@
           <t>A | 950呎 (3房)
 $3618万
 $38,084/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -43215,7 +43215,7 @@
           <t>B | 781呎 (3房)
 $2530万
 $32,399/呎
-(23年-05月)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -43223,7 +43223,7 @@
           <t>C | 903呎 (3房)
 $2888万
 $31,977/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -43238,7 +43238,7 @@
           <t>A | 950呎 (3房)
 $3154万
 $33,200/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -43246,7 +43246,7 @@
           <t>B | 781呎 (3房)
 $2550万
 $32,650/呎
-(23年-03月)</t>
+(23年-03月-13日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -43254,7 +43254,7 @@
           <t>C | 903呎 (3房)
 $2938万
 $32,538/呎
-(23年-05月)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -43269,7 +43269,7 @@
           <t>A | 950呎 (3房)
 $3480万
 $36,628/呎
-(22年-12月)</t>
+(22年-12月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -43277,7 +43277,7 @@
           <t>B | 781呎 (3房)
 $2534万
 $32,445/呎
-(23年-03月)</t>
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -43285,7 +43285,7 @@
           <t>C | 903呎 (3房)
 $3217万
 $35,626/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -43300,7 +43300,7 @@
           <t>A | 950呎 (3房)
 $3221万
 $33,902/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -43308,7 +43308,7 @@
           <t>B | 781呎 (3房)
 $2491万
 $31,900/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -43316,7 +43316,7 @@
           <t>C | 903呎 (3房)
 $2936万
 $32,514/呎
-(23年-04月)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -43331,7 +43331,7 @@
           <t>A | 950呎 (3房)
 $3200万
 $33,687/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -43339,7 +43339,7 @@
           <t>B | 781呎 (3房)
 $2476万
 $31,700/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -43347,7 +43347,7 @@
           <t>C | 903呎 (3房)
 $2835万
 $31,400/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -43362,7 +43362,7 @@
           <t>A | 950呎 (3房)
 $3564万
 $37,513/呎
-(23年-01月)</t>
+(23年-01月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -43370,7 +43370,7 @@
           <t>B | 781呎 (3房)
 $2460万
 $31,500/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -43378,7 +43378,7 @@
           <t>C | 903呎 (3房)
 $2817万
 $31,200/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -43393,7 +43393,7 @@
           <t>A | 948呎 (3房)
 $3334万
 $35,165/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -43401,7 +43401,7 @@
           <t>B | 784呎 (3房)
 $2980万
 $38,010/呎
-(22年-12月)</t>
+(22年-12月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -43409,7 +43409,7 @@
           <t>C | 902呎 (3房)
 $2742万
 $30,399/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -43424,7 +43424,7 @@
           <t>A | 948呎 (3房)
 $3268万
 $34,473/呎
-(22年-12月)</t>
+(22年-12月-12日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -43432,7 +43432,7 @@
           <t>B | 784呎 (3房)
 $2465万
 $31,444/呎
-(23年-02月)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -43440,7 +43440,7 @@
           <t>C | 902呎 (3房)
 $3120万
 $34,591/呎
-(23年-02月)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -43455,7 +43455,7 @@
           <t>A | 948呎 (3房)
 $3181万
 $33,555/呎
-(23年-02月)</t>
+(23年-02月-09日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -43463,7 +43463,7 @@
           <t>B | 784呎 (3房)
 $2446万
 $31,200/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -43471,7 +43471,7 @@
           <t>C | 902呎 (3房)
 $3028万
 $33,568/呎
-(23年-02月)</t>
+(23年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -43486,7 +43486,7 @@
           <t>A | 948呎 (3房)
 $3002万
 $31,667/呎
-(23年-02月)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -43494,7 +43494,7 @@
           <t>B | 784呎 (3房)
 $2447万
 $31,211/呎
-(23年-04月)</t>
+(23年-04月-16日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -43502,7 +43502,7 @@
           <t>C | 902呎 (3房)
 $2760万
 $30,599/呎
-(22年-12月)</t>
+(22年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
           <t>A | 948呎 (3房)
 $2967万
 $31,300/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -43525,7 +43525,7 @@
           <t>B | 784呎 (3房)
 $2564万
 $32,702/呎
-(23年-04月)</t>
+(23年-04月-02日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -43533,7 +43533,7 @@
           <t>C | 902呎 (3房)
 $2756万
 $30,550/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -43548,7 +43548,7 @@
           <t>A | 948呎 (3房)
 $2948万
 $31,100/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -43556,7 +43556,7 @@
           <t>B | 784呎 (3房)
 $2376万
 $30,300/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -43564,7 +43564,7 @@
           <t>C | 902呎 (3房)
 $3070万
 $34,034/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -43579,7 +43579,7 @@
           <t>A | 948呎 (3房)
 $2959万
 $31,209/呎
-(23年-02月)</t>
+(23年-02月-05日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -43587,7 +43587,7 @@
           <t>B | 784呎 (3房)
 $2670万
 $34,051/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -43595,7 +43595,7 @@
           <t>C | 902呎 (3房)
 $2733万
 $30,300/呎
-(23年-05月)</t>
+(23年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -43610,7 +43610,7 @@
           <t>A | 948呎 (3房)
 $2920万
 $30,800/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -43618,7 +43618,7 @@
           <t>B | 784呎 (3房)
 $2344万
 $29,900/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -43626,7 +43626,7 @@
           <t>C | 902呎 (3房)
 $2670万
 $29,600/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -43641,7 +43641,7 @@
           <t>A | 948呎 (3房)
 $3151万
 $33,235/呎
-(24年-03月)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -43649,7 +43649,7 @@
           <t>B | 784呎 (3房)
 $2398万
 $30,590/呎
-(24年-01月)</t>
+(24年-01月-16日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -43657,7 +43657,7 @@
           <t>C | 902呎 (3房)
 $2670万
 $29,596/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -43672,7 +43672,7 @@
           <t>A | 948呎 (3房)
 $2702万
 $28,500/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -43680,7 +43680,7 @@
           <t>B | 784呎 (3房)
 $2242万
 $28,600/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -43688,7 +43688,7 @@
           <t>C | 902呎 (3房)
 $2598万
 $28,800/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -43703,7 +43703,7 @@
           <t>A | 948呎 (3房)
 $2291万
 $24,163/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -43711,7 +43711,7 @@
           <t>B | 784呎 (3房)
 $1850万
 $23,596/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -43719,7 +43719,7 @@
           <t>C | 902呎 (3房)
 $2152万
 $23,856/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -43734,7 +43734,7 @@
           <t>A | 948呎 (3房)
 $2141万
 $22,582/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -43742,7 +43742,7 @@
           <t>B | 784呎 (3房)
 $1745万
 $22,260/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -43750,7 +43750,7 @@
           <t>C | 902呎 (3房)
 $2030万
 $22,506/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -43765,7 +43765,7 @@
           <t>A | 948呎 (3房)
 $2130万
 $22,469/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -43773,7 +43773,7 @@
           <t>B | 784呎 (3房)
 $1740万
 $22,194/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -43781,7 +43781,7 @@
           <t>C | 902呎 (3房)
 $2024万
 $22,438/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
           <t>A | 948呎 (3房)
 $2119万
 $22,357/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -43804,7 +43804,7 @@
           <t>B | 784呎 (3房)
 $1735万
 $22,127/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -43812,7 +43812,7 @@
           <t>C | 902呎 (3房)
 $2018万
 $22,371/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -43827,7 +43827,7 @@
           <t>A | 915呎 (3房)
 $2060万
 $22,518/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -43835,7 +43835,7 @@
           <t>B | 738呎 (3房)
 $1680万
 $22,764/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -43843,7 +43843,7 @@
           <t>C | 869呎 (3房)
 $1960万
 $22,560/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -43969,7 +43969,7 @@
           <t>A | 2729呎 (4+房)
 $16224万
 $59,449/呎
-(23年-09月)</t>
+(23年-09月-27日)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
@@ -43985,7 +43985,7 @@
           <t>A | 1523呎 (3房)
 $6543万
 $42,959/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -43993,7 +43993,7 @@
           <t>B | 1187呎 (3房)
 $4953万
 $41,725/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -44008,7 +44008,7 @@
           <t>A | 1523呎 (3房)
 $5742万
 $37,700/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -44016,7 +44016,7 @@
           <t>B | 1187呎 (3房)
 $4522万
 $38,100/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -44031,7 +44031,7 @@
           <t>A | 1523呎 (3房)
 $5966万
 $39,174/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -44039,7 +44039,7 @@
           <t>B | 1187呎 (3房)
 $5074万
 $42,743/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -44054,7 +44054,7 @@
           <t>A | 1523呎 (3房)
 $5528万
 $36,300/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -44062,7 +44062,7 @@
           <t>B | 1187呎 (3房)
 $4439万
 $37,400/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -44077,7 +44077,7 @@
           <t>A | 1523呎 (3房)
 $5498万
 $36,100/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -44085,7 +44085,7 @@
           <t>B | 1187呎 (3房)
 $4439万
 $37,400/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -44100,7 +44100,7 @@
           <t>A | 1523呎 (3房)
 $5969万
 $39,190/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -44108,7 +44108,7 @@
           <t>B | 1187呎 (3房)
 $4380万
 $36,900/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -44123,7 +44123,7 @@
           <t>A | 1523呎 (3房)
 $5986万
 $39,307/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -44131,7 +44131,7 @@
           <t>B | 1187呎 (3房)
 $4356万
 $36,700/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -44146,7 +44146,7 @@
           <t>A | 1523呎 (3房)
 $5840万
 $38,346/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -44154,7 +44154,7 @@
           <t>B | 1187呎 (3房)
 $4321万
 $36,400/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -44169,7 +44169,7 @@
           <t>A | 1523呎 (3房)
 $5457万
 $35,830/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -44177,7 +44177,7 @@
           <t>B | 1187呎 (3房)
 $4285万
 $36,100/呎
-(23年-03月)</t>
+(23年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -44192,7 +44192,7 @@
           <t>A | 1523呎 (3房)
 $5393万
 $35,410/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -44200,7 +44200,7 @@
           <t>B | 1187呎 (3房)
 $4500万
 $37,911/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -44215,7 +44215,7 @@
           <t>A | 1523呎 (3房)
 $5313万
 $34,882/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -44223,7 +44223,7 @@
           <t>B | 1135呎 (3房)
 $4214万
 $37,126/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -44238,7 +44238,7 @@
           <t>A | 1523呎 (3房)
 $5474万
 $35,942/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -44246,7 +44246,7 @@
           <t>B | 1187呎 (3房)
 $4851万
 $40,867/呎
-(23年-03月)</t>
+(23年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -44261,7 +44261,7 @@
           <t>A | 1523呎 (3房)
 $5387万
 $35,369/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -44269,7 +44269,7 @@
           <t>B | 1187呎 (3房)
 $4330万
 $36,477/呎
-(23年-02月)</t>
+(23年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -44284,7 +44284,7 @@
           <t>A | 1523呎 (3房)
 $4980万
 $32,700/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -44292,7 +44292,7 @@
           <t>B | 1187呎 (3房)
 $3960万
 $33,361/呎
-(23年-02月)</t>
+(23年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -44307,7 +44307,7 @@
           <t>A | 1523呎 (3房)
 $5364万
 $35,217/呎
-(24年-03月)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -44315,7 +44315,7 @@
           <t>B | 1187呎 (3房)
 $4095万
 $34,500/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -44330,7 +44330,7 @@
           <t>A | 1525呎 (3房)
 $4926万
 $32,300/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -44338,7 +44338,7 @@
           <t>B | 1185呎 (3房)
 $4206万
 $35,494/呎
-(23年-05月)</t>
+(23年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -44353,7 +44353,7 @@
           <t>A | 1525呎 (3房)
 $4956万
 $32,498/呎
-(23年-07月)</t>
+(23年-07月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -44361,7 +44361,7 @@
           <t>B | 1185呎 (3房)
 $4468万
 $37,705/呎
-(22年-12月)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -44376,7 +44376,7 @@
           <t>A | 1525呎 (3房)
 $5002万
 $32,800/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -44384,7 +44384,7 @@
           <t>B | 1185呎 (3房)
 $4005万
 $33,800/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -44399,7 +44399,7 @@
           <t>A | 1525呎 (3房)
 $5265万
 $34,525/呎
-(23年-02月)</t>
+(23年-02月-14日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -44407,7 +44407,7 @@
           <t>B | 1185呎 (3房)
 $4092万
 $34,531/呎
-(23年-02月)</t>
+(23年-02月-14日)</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
           <t>A | 1525呎 (3房)
 $4773万
 $31,300/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -44430,7 +44430,7 @@
           <t>B | 1185呎 (3房)
 $3922万
 $33,100/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -44445,7 +44445,7 @@
           <t>A | 1525呎 (3房)
 $5261万
 $34,497/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -44453,7 +44453,7 @@
           <t>B | 1185呎 (3房)
 $4100万
 $34,599/呎
-(23年-02月)</t>
+(23年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -44468,7 +44468,7 @@
           <t>A | 1525呎 (3房)
 $5101万
 $33,450/呎
-(22年-12月)</t>
+(22年-12月-11日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -44476,7 +44476,7 @@
           <t>B | 1185呎 (3房)
 $4337万
 $36,596/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -44491,7 +44491,7 @@
           <t>A | 1525呎 (3房)
 $4712万
 $30,900/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -44499,7 +44499,7 @@
           <t>B | 1185呎 (3房)
 $4039万
 $34,084/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -44514,7 +44514,7 @@
           <t>A | 1525呎 (3房)
 $5119万
 $33,566/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -44522,7 +44522,7 @@
           <t>B | 1185呎 (3房)
 $4317万
 $36,433/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -44537,7 +44537,7 @@
           <t>A | 1525呎 (3房)
 $4888万
 $32,050/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -44545,7 +44545,7 @@
           <t>B | 1185呎 (3房)
 $3389万
 $28,600/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -44560,7 +44560,7 @@
           <t>A | 1525呎 (3房)
 $4333万
 $28,410/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -44568,7 +44568,7 @@
           <t>B | 1185呎 (3房)
 $3300万
 $27,848/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -44583,7 +44583,7 @@
           <t>A | 1525呎 (3房)
 $4049万
 $26,552/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -44591,7 +44591,7 @@
           <t>B | 1185呎 (3房)
 $3261万
 $27,522/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -44606,7 +44606,7 @@
           <t>A | 1525呎 (3房)
 $4380万
 $28,720/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -44614,7 +44614,7 @@
           <t>B | 1185呎 (3房)
 $3072万
 $25,920/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -44629,7 +44629,7 @@
           <t>A | 1525呎 (3房)
 $4376万
 $28,692/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -44637,7 +44637,7 @@
           <t>B | 1185呎 (3房)
 $2978万
 $25,131/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -44652,7 +44652,7 @@
           <t>A | 1466呎 (3房)
 $4217万
 $28,768/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -44660,7 +44660,7 @@
           <t>B | 1146呎 (3房)
 $2904万
 $25,336/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -44792,7 +44792,7 @@
         <is>
           <t>Mansion A (Harbour Light)
 4636呎 (4+房)
-(24年-06月)
+(24年-06月-27日)
 $3.40亿
 $73,339/呎</t>
         </is>

--- a/files/九龙-启德-沄璟.xlsx
+++ b/files/九龙-启德-沄璟.xlsx
@@ -123,6 +123,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -135,12 +141,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -315,16 +315,16 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -837,7 +837,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -8826,14 +8826,14 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
         <v>13905400</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>25100</v>
+        <v>25145</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>13905400</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>25100</v>
+        <v>25145</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
@@ -37551,7 +37551,7 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -37820,12 +37820,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -37857,7 +37857,7 @@
           <t>A | 3442呎 (4+房)
 -
 -
-(待售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -37865,7 +37865,7 @@
           <t>B | 3138呎 (4+房)
 -
 -
-(待售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -37875,7 +37875,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 -
@@ -37883,7 +37883,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 -
@@ -37898,7 +37898,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 -
@@ -37906,7 +37906,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 -
@@ -37921,7 +37921,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 招标单位
@@ -37929,7 +37929,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -37944,7 +37944,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $12605万
@@ -37952,7 +37952,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -37967,7 +37967,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 2034呎 (4+房)
 $12522万
@@ -37975,7 +37975,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -37990,7 +37990,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $12446万
@@ -37998,7 +37998,7 @@
 (24年-06月-04日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38013,7 +38013,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 -
@@ -38021,7 +38021,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 -
@@ -38036,7 +38036,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $11761万
@@ -38044,7 +38044,7 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $9483万
@@ -38059,7 +38059,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $12055万
@@ -38067,7 +38067,7 @@
 (23年-03月-14日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8796万
@@ -38082,7 +38082,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $11467万
@@ -38090,7 +38090,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $9233万
@@ -38105,7 +38105,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $10557万
@@ -38113,7 +38113,7 @@
 (23年-02月-07日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38128,7 +38128,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $12038万
@@ -38136,7 +38136,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $9278万
@@ -38151,7 +38151,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $10255万
@@ -38159,7 +38159,7 @@
 (23年-02月-02日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8013万
@@ -38174,7 +38174,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $10110万
@@ -38182,7 +38182,7 @@
 (23年-01月-30日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1816呎 (4+房)
 $9054万
@@ -38197,7 +38197,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $10252万
@@ -38205,7 +38205,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8578万
@@ -38220,7 +38220,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $10085万
@@ -38228,7 +38228,7 @@
 (24年-11月-24日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8929万
@@ -38243,7 +38243,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $10117万
@@ -38251,7 +38251,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 1816呎 (4+房)
 $8690万
@@ -38266,7 +38266,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9855万
@@ -38274,7 +38274,7 @@
 (25年-11月-17日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8308万
@@ -38289,7 +38289,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9587万
@@ -38297,7 +38297,7 @@
 (23年-02月-14日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8207万
@@ -38312,7 +38312,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9324万
@@ -38320,7 +38320,7 @@
 (23年-01月-30日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8477万
@@ -38335,7 +38335,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9542万
@@ -38343,7 +38343,7 @@
 (25年-09月-28日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7386万
@@ -38358,7 +38358,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9420万
@@ -38366,7 +38366,7 @@
 (23年-01月-19日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7939万
@@ -38381,7 +38381,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $8403万
@@ -38389,7 +38389,7 @@
 (23年-01月-12日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7315万
@@ -38404,7 +38404,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $8456万
@@ -38412,7 +38412,7 @@
 (23年-03月-01日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7143万
@@ -38427,7 +38427,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9271万
@@ -38435,7 +38435,7 @@
 (25年-10月-22日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8182万
@@ -38450,7 +38450,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9703万
@@ -38458,7 +38458,7 @@
 (24年-04月-08日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7750万
@@ -38473,7 +38473,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9127万
@@ -38481,7 +38481,7 @@
 (23年-03月-14日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7696万
@@ -38496,7 +38496,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 $9427万
@@ -38504,7 +38504,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7684万
@@ -38519,7 +38519,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 $8658万
@@ -38527,7 +38527,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 1797呎 (4+房)
 $7178万
@@ -38621,12 +38621,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -38658,10 +38658,10 @@
           <t>A | 3406呎 (4+房)
 -
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 3137呎 (4+房)
 招标单位
@@ -38676,7 +38676,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 -
@@ -38684,7 +38684,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 -
@@ -38699,7 +38699,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 -
@@ -38707,7 +38707,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 -
@@ -38722,7 +38722,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 招标单位
@@ -38730,7 +38730,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38745,7 +38745,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 招标单位
@@ -38753,7 +38753,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38768,7 +38768,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $9704万
@@ -38776,7 +38776,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $9146万
@@ -38791,7 +38791,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 招标单位
@@ -38799,7 +38799,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38814,7 +38814,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 -
@@ -38822,7 +38822,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 -
@@ -38837,7 +38837,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 招标单位
@@ -38845,7 +38845,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8415万
@@ -38860,7 +38860,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $9434万
@@ -38868,7 +38868,7 @@
 (24年-11月-12日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38883,7 +38883,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $9490万
@@ -38891,7 +38891,7 @@
 (26年-03月-24日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38906,7 +38906,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8880万
@@ -38914,7 +38914,7 @@
 (23年-02月-12日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38929,7 +38929,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $9295万
@@ -38937,7 +38937,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38952,7 +38952,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $9015万
@@ -38960,7 +38960,7 @@
 (23年-07月-05日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1816呎 (4+房)
 $9086万
@@ -38975,7 +38975,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $9017万
@@ -38983,7 +38983,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38998,7 +38998,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8552万
@@ -39006,7 +39006,7 @@
 (25年-02月-16日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8265万
@@ -39021,7 +39021,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8837万
@@ -39029,7 +39029,7 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -39044,7 +39044,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8302万
@@ -39052,7 +39052,7 @@
 (24年-09月-10日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8103万
@@ -39067,7 +39067,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7865万
@@ -39075,7 +39075,7 @@
 (24年-08月-06日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7667万
@@ -39090,7 +39090,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7770万
@@ -39098,7 +39098,7 @@
 (24年-08月-06日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7574万
@@ -39113,7 +39113,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8062万
@@ -39121,7 +39121,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8054万
@@ -39136,7 +39136,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8319万
@@ -39144,7 +39144,7 @@
 (24年-05月-22日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7630万
@@ -39159,7 +39159,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7882万
@@ -39167,7 +39167,7 @@
 (24年-05月-15日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7904万
@@ -39182,7 +39182,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7470万
@@ -39190,7 +39190,7 @@
 (23年-07月-05日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7860万
@@ -39205,7 +39205,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8131万
@@ -39213,7 +39213,7 @@
 (25年-11月-09日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7800万
@@ -39228,7 +39228,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $8104万
@@ -39236,7 +39236,7 @@
 (25年-11月-09日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $8167万
@@ -39251,7 +39251,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7708万
@@ -39259,7 +39259,7 @@
 (24年-05月-16日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7532万
@@ -39274,7 +39274,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7292万
@@ -39282,7 +39282,7 @@
 (24年-06月-19日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 $7704万
@@ -39297,7 +39297,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 1909呎 (4+房)
 $7576万
@@ -39305,7 +39305,7 @@
 (24年-11月-10日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 1816呎 (4+房)
 $7996万
@@ -39320,7 +39320,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 1828呎 (4+房)
 $7534万
@@ -39328,7 +39328,7 @@
 (25年-11月-10日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 1797呎 (4+房)
 $7380万
@@ -39466,7 +39466,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 1129呎 (3房)
 $5215万
@@ -39474,7 +39474,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 1334呎 (3房)
 $3869万
@@ -39491,7 +39491,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1546万
@@ -39499,15 +39499,15 @@
 (25年-08月-25日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 553呎 (2房)
 $1391万
-$25,100/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
+$25,145/呎
+(26年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39515,7 +39515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39530,7 +39530,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1512万
@@ -39538,7 +39538,7 @@
 (25年-08月-26日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1363万
@@ -39546,7 +39546,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39554,7 +39554,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39569,7 +39569,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 -
@@ -39577,7 +39577,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -39585,7 +39585,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39593,7 +39593,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39608,7 +39608,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1489万
@@ -39616,7 +39616,7 @@
 (25年-05月-05日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1324万
@@ -39624,7 +39624,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39632,7 +39632,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39647,7 +39647,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1482万
@@ -39655,7 +39655,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1319万
@@ -39663,7 +39663,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39671,7 +39671,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39686,7 +39686,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1474万
@@ -39694,7 +39694,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1341万
@@ -39702,7 +39702,7 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39710,7 +39710,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39725,7 +39725,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1467万
@@ -39733,7 +39733,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1335万
@@ -39741,7 +39741,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39749,7 +39749,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39764,7 +39764,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1460万
@@ -39772,7 +39772,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1319万
@@ -39780,7 +39780,7 @@
 (26年-06月-14日)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39788,7 +39788,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39803,7 +39803,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1469万
@@ -39811,7 +39811,7 @@
 (24年-10月-28日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1285万
@@ -39819,7 +39819,7 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1196万
@@ -39827,7 +39827,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39842,7 +39842,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1438万
@@ -39850,7 +39850,7 @@
 (24年-11月-06日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1274万
@@ -39858,7 +39858,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1191万
@@ -39866,7 +39866,7 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39881,7 +39881,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1431万
@@ -39889,7 +39889,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1269万
@@ -39897,7 +39897,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1186万
@@ -39905,7 +39905,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39920,7 +39920,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1424万
@@ -39928,7 +39928,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1302万
@@ -39936,7 +39936,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39944,7 +39944,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39959,7 +39959,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1417万
@@ -39967,7 +39967,7 @@
 (25年-05月-05日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1280万
@@ -39975,7 +39975,7 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -39983,7 +39983,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -39998,7 +39998,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1410万
@@ -40006,7 +40006,7 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1274万
@@ -40014,7 +40014,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40022,7 +40022,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40037,7 +40037,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1403万
@@ -40045,7 +40045,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1285万
@@ -40053,7 +40053,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40061,7 +40061,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40076,7 +40076,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1411万
@@ -40084,7 +40084,7 @@
 (24年-04月-28日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1280万
@@ -40092,7 +40092,7 @@
 (26年-06月-21日)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40100,7 +40100,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40115,7 +40115,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1389万
@@ -40123,7 +40123,7 @@
 (24年-12月-03日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1274万
@@ -40131,7 +40131,7 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40139,7 +40139,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40154,7 +40154,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1382万
@@ -40162,7 +40162,7 @@
 (24年-12月-30日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1274万
@@ -40170,7 +40170,7 @@
 (26年-07月-01日)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40178,7 +40178,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40193,7 +40193,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1368万
@@ -40201,7 +40201,7 @@
 (24年-10月-28日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1258万
@@ -40209,7 +40209,7 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1155万
@@ -40217,7 +40217,7 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40232,7 +40232,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1361万
@@ -40240,7 +40240,7 @@
 (24年-11月-06日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1252万
@@ -40248,7 +40248,7 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1150万
@@ -40256,7 +40256,7 @@
 (26年-07月-05日)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40271,7 +40271,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1355万
@@ -40279,7 +40279,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1295万
@@ -40287,7 +40287,7 @@
 (26年-06月-21日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 招标单位
@@ -40295,7 +40295,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40310,7 +40310,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1348万
@@ -40318,7 +40318,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 553呎 (2房)
 $1252万
@@ -40326,7 +40326,7 @@
 (26年-07月-12日)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40334,7 +40334,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40349,7 +40349,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1341万
@@ -40357,7 +40357,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1246万
@@ -40365,7 +40365,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40373,7 +40373,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40388,7 +40388,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1335万
@@ -40396,7 +40396,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1235万
@@ -40404,7 +40404,7 @@
 (26年-06月-21日)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40412,7 +40412,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40427,7 +40427,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1247万
@@ -40435,7 +40435,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -40443,7 +40443,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40451,7 +40451,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40466,7 +40466,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1210万
@@ -40474,7 +40474,7 @@
 (25年-08月-27日)</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -40482,7 +40482,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40490,7 +40490,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40505,7 +40505,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1198万
@@ -40513,7 +40513,7 @@
 (25年-08月-26日)</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -40521,7 +40521,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40529,7 +40529,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40544,7 +40544,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1195万
@@ -40552,7 +40552,7 @@
 (25年-08月-31日)</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -40560,7 +40560,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40568,7 +40568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40583,7 +40583,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1191万
@@ -40591,7 +40591,7 @@
 (25年-09月-21日)</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -40599,7 +40599,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40607,7 +40607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40622,7 +40622,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 539呎 (2房)
 $1197万
@@ -40630,7 +40630,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 -
@@ -40638,7 +40638,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 -
@@ -40646,7 +40646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 -
@@ -40778,7 +40778,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1109呎 (3房)
 招标单位
@@ -40795,7 +40795,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1799万
@@ -40803,7 +40803,7 @@
 (25年-08月-21日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1423万
@@ -40811,7 +40811,7 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1551万
@@ -40826,7 +40826,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1766万
@@ -40834,7 +40834,7 @@
 (25年-08月-07日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1396万
@@ -40842,7 +40842,7 @@
 (25年-12月-07日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1522万
@@ -40857,7 +40857,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1746万
@@ -40865,7 +40865,7 @@
 (25年-08月-31日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1381万
@@ -40873,7 +40873,7 @@
 (25年-10月-15日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1505万
@@ -40888,7 +40888,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1735万
@@ -40896,7 +40896,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1371万
@@ -40904,7 +40904,7 @@
 (24年-07月-16日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 1644呎 (2房)
 $1496万
@@ -40919,7 +40919,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1726万
@@ -40927,7 +40927,7 @@
 (25年-06月-16日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1364万
@@ -40935,7 +40935,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1488万
@@ -40950,7 +40950,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1717万
@@ -40958,7 +40958,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1357万
@@ -40966,7 +40966,7 @@
 (25年-07月-27日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1481万
@@ -40981,7 +40981,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1709万
@@ -40989,7 +40989,7 @@
 (25年-06月-02日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1350万
@@ -40997,7 +40997,7 @@
 (24年-05月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1474万
@@ -41012,7 +41012,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1700万
@@ -41020,7 +41020,7 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1343万
@@ -41028,7 +41028,7 @@
 (24年-11月-24日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1466万
@@ -41043,7 +41043,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1692万
@@ -41051,7 +41051,7 @@
 (24年-11月-24日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1337万
@@ -41059,7 +41059,7 @@
 (24年-11月-18日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1459万
@@ -41074,7 +41074,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1675万
@@ -41082,7 +41082,7 @@
 (25年-02月-27日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1324万
@@ -41090,7 +41090,7 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1445万
@@ -41105,7 +41105,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1667万
@@ -41113,7 +41113,7 @@
 (24年-06月-06日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1317万
@@ -41121,7 +41121,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1437万
@@ -41136,7 +41136,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1659万
@@ -41144,7 +41144,7 @@
 (24年-11月-17日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1310万
@@ -41152,7 +41152,7 @@
 (24年-09月-16日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1430万
@@ -41167,7 +41167,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1650万
@@ -41175,7 +41175,7 @@
 (24年-05月-15日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1304万
@@ -41183,7 +41183,7 @@
 (24年-09月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1423万
@@ -41198,7 +41198,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1642万
@@ -41206,7 +41206,7 @@
 (24年-08月-05日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1297万
@@ -41214,7 +41214,7 @@
 (24年-06月-05日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1416万
@@ -41229,7 +41229,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 659呎 (2房)
 $1634万
@@ -41237,7 +41237,7 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
 $1291万
@@ -41245,7 +41245,7 @@
 (24年-07月-30日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1409万
@@ -41260,7 +41260,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1618万
@@ -41268,7 +41268,7 @@
 (24年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1292万
@@ -41276,7 +41276,7 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1402万
@@ -41291,7 +41291,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1610万
@@ -41299,7 +41299,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1285万
@@ -41307,7 +41307,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1395万
@@ -41322,7 +41322,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1602万
@@ -41330,7 +41330,7 @@
 (24年-05月-12日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1279万
@@ -41338,7 +41338,7 @@
 (25年-03月-23日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1388万
@@ -41353,7 +41353,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1587万
@@ -41361,7 +41361,7 @@
 (24年-10月-28日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1266万
@@ -41369,7 +41369,7 @@
 (24年-12月-05日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1374万
@@ -41384,7 +41384,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1579万
@@ -41392,7 +41392,7 @@
 (24年-07月-28日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1260万
@@ -41400,7 +41400,7 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1368万
@@ -41415,7 +41415,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1571万
@@ -41423,7 +41423,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1254万
@@ -41431,7 +41431,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1376万
@@ -41446,7 +41446,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1563万
@@ -41454,7 +41454,7 @@
 (24年-10月-28日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1248万
@@ -41462,7 +41462,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1354万
@@ -41477,7 +41477,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1555万
@@ -41485,7 +41485,7 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1241万
@@ -41493,7 +41493,7 @@
 (24年-10月-28日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1347万
@@ -41508,7 +41508,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1547万
@@ -41516,7 +41516,7 @@
 (25年-03月-03日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1235万
@@ -41524,7 +41524,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1355万
@@ -41539,7 +41539,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1429万
@@ -41547,7 +41547,7 @@
 (25年-06月-03日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1158万
@@ -41555,7 +41555,7 @@
 (25年-04月-27日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1250万
@@ -41570,7 +41570,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1361万
@@ -41578,7 +41578,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1103万
@@ -41586,7 +41586,7 @@
 (25年-05月-06日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1191万
@@ -41601,7 +41601,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1335万
@@ -41609,7 +41609,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1081万
@@ -41617,7 +41617,7 @@
 (25年-08月-25日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1179万
@@ -41632,7 +41632,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1331万
@@ -41640,7 +41640,7 @@
 (25年-04月-06日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1078万
@@ -41648,7 +41648,7 @@
 (25年-05月-06日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1176万
@@ -41663,7 +41663,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 656呎 (2房)
 $1327万
@@ -41671,7 +41671,7 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 526呎 (2房)
 $1075万
@@ -41679,7 +41679,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 568呎 (2房)
 $1172万
@@ -41694,7 +41694,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 618呎 (2房)
 $1259万
@@ -41702,7 +41702,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 488呎 (2房)
 $1014万
@@ -41710,7 +41710,7 @@
 (25年-03月-17日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 530呎 (2房)
 $1166万
@@ -41842,7 +41842,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1994呎 (4+房)
 招标单位
@@ -41859,7 +41859,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $3070万
@@ -41867,7 +41867,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1884万
@@ -41875,7 +41875,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1978万
@@ -41890,7 +41890,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $3043万
@@ -41898,7 +41898,7 @@
 (25年-11月-16日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1844万
@@ -41906,7 +41906,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1941万
@@ -41921,7 +41921,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 900呎 (3房)
 $3043万
@@ -41929,7 +41929,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1827万
@@ -41937,7 +41937,7 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1916万
@@ -41952,7 +41952,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2935万
@@ -41960,7 +41960,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1816万
@@ -41968,7 +41968,7 @@
 (25年-08月-20日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1904万
@@ -41983,7 +41983,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2946万
@@ -41991,7 +41991,7 @@
 (24年-04月-15日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1805万
@@ -41999,7 +41999,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1914万
@@ -42014,7 +42014,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2899万
@@ -42022,7 +42022,7 @@
 (24年-04月-15日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1794万
@@ -42030,7 +42030,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1902万
@@ -42045,7 +42045,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2935万
@@ -42053,7 +42053,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1782万
@@ -42061,7 +42061,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1870万
@@ -42076,7 +42076,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2862万
@@ -42084,7 +42084,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1771万
@@ -42092,7 +42092,7 @@
 (25年-08月-06日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1859万
@@ -42107,7 +42107,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2872万
@@ -42115,7 +42115,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1760万
@@ -42123,7 +42123,7 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1848万
@@ -42138,7 +42138,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2946万
@@ -42146,7 +42146,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1779万
@@ -42154,7 +42154,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1828万
@@ -42169,7 +42169,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $3180万
@@ -42177,7 +42177,7 @@
 (24年-04月-14日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1687万
@@ -42185,7 +42185,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1781万
@@ -42200,7 +42200,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2781万
@@ -42208,7 +42208,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1719万
@@ -42216,7 +42216,7 @@
 (24年-05月-07日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1790万
@@ -42231,7 +42231,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2798万
@@ -42239,7 +42239,7 @@
 (24年-03月-18日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1709万
@@ -42247,7 +42247,7 @@
 (24年-08月-13日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1780万
@@ -42262,7 +42262,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2745万
@@ -42270,7 +42270,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1699万
@@ -42278,7 +42278,7 @@
 (24年-06月-26日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1769万
@@ -42293,7 +42293,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 903呎 (3房)
 $2764万
@@ -42301,7 +42301,7 @@
 (24年-04月-02日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 564呎 (2房)
 $1689万
@@ -42309,7 +42309,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 620呎 (2房)
 $1759万
@@ -42324,7 +42324,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2867万
@@ -42332,7 +42332,7 @@
 (24年-04月-04日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1725万
@@ -42340,7 +42340,7 @@
 (24年-05月-15日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1726万
@@ -42355,7 +42355,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2697万
@@ -42363,7 +42363,7 @@
 (24年-04月-02日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1677万
@@ -42371,7 +42371,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1716万
@@ -42386,7 +42386,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2679万
@@ -42394,7 +42394,7 @@
 (24年-04月-15日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1667万
@@ -42402,7 +42402,7 @@
 (24年-08月-19日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1725万
@@ -42417,7 +42417,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2661万
@@ -42425,7 +42425,7 @@
 (24年-04月-08日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1627万
@@ -42433,7 +42433,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1706万
@@ -42448,7 +42448,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2634万
@@ -42456,7 +42456,7 @@
 (24年-03月-26日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1617万
@@ -42464,7 +42464,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1677万
@@ -42479,7 +42479,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2713万
@@ -42487,7 +42487,7 @@
 (23年-10月-19日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1590万
@@ -42495,7 +42495,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1700万
@@ -42510,7 +42510,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2970万
@@ -42518,7 +42518,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1598万
@@ -42526,7 +42526,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1657万
@@ -42541,7 +42541,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2589万
@@ -42549,7 +42549,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1588万
@@ -42557,7 +42557,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1647万
@@ -42572,7 +42572,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2571万
@@ -42580,7 +42580,7 @@
 (24年-04月-21日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1562万
@@ -42588,7 +42588,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1637万
@@ -42603,7 +42603,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2526万
@@ -42611,7 +42611,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1442万
@@ -42619,7 +42619,7 @@
 (25年-03月-25日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1530万
@@ -42634,7 +42634,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $2089万
@@ -42642,7 +42642,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1299万
@@ -42650,7 +42650,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1391万
@@ -42665,7 +42665,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $1989万
@@ -42673,7 +42673,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1238万
@@ -42681,7 +42681,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1337万
@@ -42696,7 +42696,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $1983万
@@ -42704,7 +42704,7 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1234万
@@ -42712,7 +42712,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1333万
@@ -42727,7 +42727,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 902呎 (3房)
 $1977万
@@ -42735,7 +42735,7 @@
 (25年-09月-03日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 $1230万
@@ -42743,7 +42743,7 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 619呎 (2房)
 $1329万
@@ -42758,7 +42758,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 869呎 (3房)
 $1921万
@@ -42766,7 +42766,7 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 529呎 (2房)
 $1165万
@@ -42774,7 +42774,7 @@
 (25年-03月-25日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 597呎 (2房)
 $1292万
@@ -42906,7 +42906,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 2103呎 (4+房)
 招标单位
@@ -42923,7 +42923,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3515万
@@ -42931,7 +42931,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2761万
@@ -42939,7 +42939,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3133万
@@ -42954,7 +42954,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3397万
@@ -42962,7 +42962,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2706万
@@ -42970,7 +42970,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3101万
@@ -42985,7 +42985,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3473万
@@ -42993,7 +42993,7 @@
 (24年-04月-10日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2773万
@@ -43001,7 +43001,7 @@
 (24年-04月-10日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3043万
@@ -43016,7 +43016,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3914万
@@ -43024,7 +43024,7 @@
 (23年-03月-09日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2666万
@@ -43032,7 +43032,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3025万
@@ -43047,7 +43047,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3539万
@@ -43055,7 +43055,7 @@
 (23年-03月-05日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2646万
@@ -43063,7 +43063,7 @@
 (24年-04月-04日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3010万
@@ -43078,7 +43078,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3711万
@@ -43086,7 +43086,7 @@
 (23年-03月-05日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2609万
@@ -43094,7 +43094,7 @@
 (24年-04月-07日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2989万
@@ -43109,7 +43109,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3671万
@@ -43117,7 +43117,7 @@
 (23年-03月-20日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2708万
@@ -43125,7 +43125,7 @@
 (24年-04月-10日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3340万
@@ -43140,7 +43140,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3223万
@@ -43148,7 +43148,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2708万
@@ -43156,7 +43156,7 @@
 (24年-04月-11日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2953万
@@ -43171,7 +43171,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3211万
@@ -43179,7 +43179,7 @@
 (25年-11月-19日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2562万
@@ -43187,7 +43187,7 @@
 (25年-12月-29日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3046万
@@ -43202,7 +43202,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3618万
@@ -43210,7 +43210,7 @@
 (23年-02月-01日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2530万
@@ -43218,7 +43218,7 @@
 (23年-05月-24日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2888万
@@ -43233,7 +43233,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3154万
@@ -43241,7 +43241,7 @@
 (25年-08月-24日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2550万
@@ -43249,7 +43249,7 @@
 (23年-03月-13日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2938万
@@ -43264,7 +43264,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3480万
@@ -43272,7 +43272,7 @@
 (22年-12月-12日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2534万
@@ -43280,7 +43280,7 @@
 (23年-03月-06日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $3217万
@@ -43295,7 +43295,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3221万
@@ -43303,7 +43303,7 @@
 (23年-02月-01日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2491万
@@ -43311,7 +43311,7 @@
 (25年-11月-23日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2936万
@@ -43326,7 +43326,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3200万
@@ -43334,7 +43334,7 @@
 (23年-02月-01日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2476万
@@ -43342,7 +43342,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2835万
@@ -43357,7 +43357,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 950呎 (3房)
 $3564万
@@ -43365,7 +43365,7 @@
 (23年-01月-12日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
 $2460万
@@ -43373,7 +43373,7 @@
 (25年-12月-14日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 903呎 (3房)
 $2817万
@@ -43388,7 +43388,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $3334万
@@ -43396,7 +43396,7 @@
 (22年-12月-07日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2980万
@@ -43404,7 +43404,7 @@
 (22年-12月-27日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2742万
@@ -43419,7 +43419,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $3268万
@@ -43427,7 +43427,7 @@
 (22年-12月-12日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2465万
@@ -43435,7 +43435,7 @@
 (23年-02月-08日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $3120万
@@ -43450,7 +43450,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $3181万
@@ -43458,7 +43458,7 @@
 (23年-02月-09日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2446万
@@ -43466,7 +43466,7 @@
 (22年-12月-07日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $3028万
@@ -43481,7 +43481,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $3002万
@@ -43489,7 +43489,7 @@
 (23年-02月-06日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2447万
@@ -43497,7 +43497,7 @@
 (23年-04月-16日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2760万
@@ -43512,7 +43512,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2967万
@@ -43520,7 +43520,7 @@
 (25年-10月-29日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2564万
@@ -43528,7 +43528,7 @@
 (23年-04月-02日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2756万
@@ -43543,7 +43543,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2948万
@@ -43551,7 +43551,7 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2376万
@@ -43559,7 +43559,7 @@
 (22年-12月-07日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $3070万
@@ -43574,7 +43574,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2959万
@@ -43582,7 +43582,7 @@
 (23年-02月-05日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2670万
@@ -43590,7 +43590,7 @@
 (22年-12月-07日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2733万
@@ -43605,7 +43605,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2920万
@@ -43613,7 +43613,7 @@
 (25年-10月-07日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2344万
@@ -43621,7 +43621,7 @@
 (25年-10月-29日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2670万
@@ -43636,7 +43636,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $3151万
@@ -43644,7 +43644,7 @@
 (24年-03月-12日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2398万
@@ -43652,7 +43652,7 @@
 (24年-01月-16日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2670万
@@ -43667,7 +43667,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2702万
@@ -43675,7 +43675,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $2242万
@@ -43683,7 +43683,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2598万
@@ -43698,7 +43698,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2291万
@@ -43706,7 +43706,7 @@
 (25年-03月-10日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $1850万
@@ -43714,7 +43714,7 @@
 (25年-03月-23日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2152万
@@ -43729,7 +43729,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2141万
@@ -43737,7 +43737,7 @@
 (25年-04月-15日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $1745万
@@ -43745,7 +43745,7 @@
 (25年-04月-15日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2030万
@@ -43760,7 +43760,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2130万
@@ -43768,7 +43768,7 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $1740万
@@ -43776,7 +43776,7 @@
 (25年-06月-16日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2024万
@@ -43791,7 +43791,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 948呎 (3房)
 $2119万
@@ -43799,7 +43799,7 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 $1735万
@@ -43807,7 +43807,7 @@
 (25年-06月-16日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 902呎 (3房)
 $2018万
@@ -43822,7 +43822,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $2060万
@@ -43830,7 +43830,7 @@
 (25年-09月-21日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 738呎 (3房)
 $1680万
@@ -43838,7 +43838,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 869呎 (3房)
 $1960万
@@ -43964,7 +43964,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 2729呎 (4+房)
 $16224万
@@ -43980,7 +43980,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $6543万
@@ -43988,7 +43988,7 @@
 (24年-12月-29日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4953万
@@ -44003,7 +44003,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5742万
@@ -44011,7 +44011,7 @@
 (25年-09月-22日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4522万
@@ -44026,7 +44026,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5966万
@@ -44034,7 +44034,7 @@
 (25年-10月-14日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $5074万
@@ -44049,7 +44049,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5528万
@@ -44057,7 +44057,7 @@
 (25年-01月-27日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4439万
@@ -44072,7 +44072,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5498万
@@ -44080,7 +44080,7 @@
 (24年-12月-17日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4439万
@@ -44095,7 +44095,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5969万
@@ -44103,7 +44103,7 @@
 (24年-10月-03日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4380万
@@ -44118,7 +44118,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5986万
@@ -44126,7 +44126,7 @@
 (24年-04月-14日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4356万
@@ -44141,7 +44141,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5840万
@@ -44149,7 +44149,7 @@
 (24年-11月-19日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4321万
@@ -44164,7 +44164,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5457万
@@ -44172,7 +44172,7 @@
 (24年-11月-19日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4285万
@@ -44187,7 +44187,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5393万
@@ -44195,7 +44195,7 @@
 (24年-11月-19日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4500万
@@ -44210,7 +44210,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5313万
@@ -44218,7 +44218,7 @@
 (23年-03月-02日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 1135呎 (3房)
 $4214万
@@ -44233,7 +44233,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5474万
@@ -44241,7 +44241,7 @@
 (24年-11月-11日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4851万
@@ -44256,7 +44256,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5387万
@@ -44264,7 +44264,7 @@
 (24年-10月-09日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4330万
@@ -44279,7 +44279,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $4980万
@@ -44287,7 +44287,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $3960万
@@ -44302,7 +44302,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 1523呎 (3房)
 $5364万
@@ -44310,7 +44310,7 @@
 (24年-03月-12日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1187呎 (3房)
 $4095万
@@ -44325,7 +44325,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4926万
@@ -44333,7 +44333,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4206万
@@ -44348,7 +44348,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4956万
@@ -44356,7 +44356,7 @@
 (23年-07月-10日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4468万
@@ -44371,7 +44371,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $5002万
@@ -44379,7 +44379,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4005万
@@ -44394,7 +44394,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $5265万
@@ -44402,7 +44402,7 @@
 (23年-02月-14日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4092万
@@ -44417,7 +44417,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4773万
@@ -44425,7 +44425,7 @@
 (24年-05月-22日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $3922万
@@ -44440,7 +44440,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $5261万
@@ -44448,7 +44448,7 @@
 (25年-11月-10日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4100万
@@ -44463,7 +44463,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $5101万
@@ -44471,7 +44471,7 @@
 (22年-12月-11日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4337万
@@ -44486,7 +44486,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4712万
@@ -44494,7 +44494,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4039万
@@ -44509,7 +44509,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $5119万
@@ -44517,7 +44517,7 @@
 (25年-09月-28日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $4317万
@@ -44532,7 +44532,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4888万
@@ -44540,7 +44540,7 @@
 (24年-11月-25日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $3389万
@@ -44555,7 +44555,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4333万
@@ -44563,7 +44563,7 @@
 (25年-04月-15日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $3300万
@@ -44578,7 +44578,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4049万
@@ -44586,7 +44586,7 @@
 (25年-11月-10日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $3261万
@@ -44601,7 +44601,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4380万
@@ -44609,7 +44609,7 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $3072万
@@ -44624,7 +44624,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 1525呎 (3房)
 $4376万
@@ -44632,7 +44632,7 @@
 (26年-01月-21日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 1185呎 (3房)
 $2978万
@@ -44647,7 +44647,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 1466呎 (3房)
 $4217万
@@ -44655,7 +44655,7 @@
 (26年-03月-22日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 1146呎 (3房)
 $2904万
@@ -44750,12 +44750,12 @@
       </c>
       <c r="E3" s="29" t="inlineStr">
         <is>
-          <t>0 套</t>
+          <t>2 套</t>
         </is>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>4 套</t>
+          <t>2 套</t>
         </is>
       </c>
     </row>
@@ -44788,7 +44788,7 @@
         </is>
       </c>
       <c r="B6" s="30" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Mansion A (Harbour Light)
 4636呎 (4+房)
@@ -44809,7 +44809,7 @@
         <is>
           <t>Mansion B (Harbour Breeze)
 4294呎 (4+房)
-(待售)
+(暂停销售)
 暂无价格
 暂无呎价</t>
         </is>
@@ -44825,7 +44825,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr"/>
       <c r="C8" s="30" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Mansion C (Harbour Wave)
 4850呎 (4+房)
